--- a/assets/Listados/CGS - 3414936 - 2026.xlsx
+++ b/assets/Listados/CGS - 3414936 - 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos\Documents\Bot_sena_seguimiento\assets\Listados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C6DBD9-0228-4FDE-85F0-6AA8DF8AFB00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342094AA-F4F1-484A-A2CB-5462309145DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ASISTENCIA " sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="294">
   <si>
     <r>
       <rPr>
@@ -2816,23 +2816,84 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="41" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -2841,77 +2902,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2925,81 +2926,92 @@
     <xf numFmtId="0" fontId="33" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3012,18 +3024,6 @@
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4425,125 +4425,125 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:129" ht="24.75" customHeight="1">
-      <c r="A1" s="154"/>
-      <c r="B1" s="123"/>
-      <c r="C1" s="155" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="159" t="s">
+      <c r="A1" s="190"/>
+      <c r="B1" s="191"/>
+      <c r="C1" s="194" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="191"/>
+      <c r="G1" s="170" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="135"/>
-      <c r="U1" s="134"/>
-      <c r="V1" s="134"/>
-      <c r="W1" s="134"/>
-      <c r="X1" s="133"/>
-      <c r="Y1" s="134"/>
-      <c r="Z1" s="134"/>
-      <c r="AA1" s="134"/>
-      <c r="AB1" s="135"/>
-      <c r="AC1" s="134"/>
-      <c r="AD1" s="134"/>
-      <c r="AE1" s="134"/>
-      <c r="AF1" s="134"/>
-      <c r="AG1" s="134"/>
-      <c r="AH1" s="134"/>
-      <c r="AI1" s="134"/>
-      <c r="AJ1" s="134"/>
-      <c r="AK1" s="136"/>
-      <c r="AL1" s="186"/>
-      <c r="AM1" s="134"/>
-      <c r="AN1" s="134"/>
-      <c r="AO1" s="134"/>
-      <c r="AP1" s="134"/>
-      <c r="AQ1" s="134"/>
-      <c r="AR1" s="134"/>
-      <c r="AS1" s="134"/>
-      <c r="AT1" s="134"/>
-      <c r="AU1" s="187"/>
-      <c r="AV1" s="134"/>
-      <c r="AW1" s="134"/>
-      <c r="AX1" s="134"/>
-      <c r="AY1" s="134"/>
-      <c r="AZ1" s="134"/>
-      <c r="BA1" s="134"/>
-      <c r="BB1" s="134"/>
-      <c r="BC1" s="134"/>
-      <c r="BD1" s="134"/>
-      <c r="BE1" s="134"/>
-      <c r="BF1" s="134"/>
-      <c r="BG1" s="134"/>
-      <c r="BH1" s="134"/>
-      <c r="BI1" s="134"/>
-      <c r="BJ1" s="134"/>
-      <c r="BK1" s="134"/>
-      <c r="BL1" s="134"/>
-      <c r="BM1" s="134"/>
-      <c r="BN1" s="134"/>
-      <c r="BO1" s="134"/>
-      <c r="BP1" s="134"/>
-      <c r="BQ1" s="134"/>
-      <c r="BR1" s="134"/>
-      <c r="BS1" s="134"/>
-      <c r="BT1" s="134"/>
-      <c r="BU1" s="134"/>
-      <c r="BV1" s="188"/>
-      <c r="BW1" s="134"/>
-      <c r="BX1" s="134"/>
-      <c r="BY1" s="134"/>
-      <c r="BZ1" s="134"/>
-      <c r="CA1" s="134"/>
-      <c r="CB1" s="134"/>
-      <c r="CC1" s="134"/>
-      <c r="CD1" s="134"/>
-      <c r="CE1" s="134"/>
-      <c r="CF1" s="134"/>
-      <c r="CG1" s="134"/>
-      <c r="CH1" s="134"/>
-      <c r="CI1" s="134"/>
-      <c r="CJ1" s="134"/>
-      <c r="CK1" s="134"/>
-      <c r="CL1" s="134"/>
-      <c r="CM1" s="134"/>
-      <c r="CN1" s="134"/>
-      <c r="CO1" s="134"/>
-      <c r="CP1" s="134"/>
-      <c r="CQ1" s="134"/>
-      <c r="CR1" s="136"/>
-      <c r="CS1" s="190" t="s">
+      <c r="H1" s="124"/>
+      <c r="I1" s="124"/>
+      <c r="J1" s="124"/>
+      <c r="K1" s="124"/>
+      <c r="L1" s="124"/>
+      <c r="M1" s="124"/>
+      <c r="N1" s="124"/>
+      <c r="O1" s="124"/>
+      <c r="P1" s="177"/>
+      <c r="Q1" s="124"/>
+      <c r="R1" s="124"/>
+      <c r="S1" s="174"/>
+      <c r="T1" s="178"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="179"/>
+      <c r="Y1" s="119"/>
+      <c r="Z1" s="119"/>
+      <c r="AA1" s="119"/>
+      <c r="AB1" s="178"/>
+      <c r="AC1" s="119"/>
+      <c r="AD1" s="119"/>
+      <c r="AE1" s="119"/>
+      <c r="AF1" s="119"/>
+      <c r="AG1" s="119"/>
+      <c r="AH1" s="119"/>
+      <c r="AI1" s="119"/>
+      <c r="AJ1" s="119"/>
+      <c r="AK1" s="122"/>
+      <c r="AL1" s="118"/>
+      <c r="AM1" s="119"/>
+      <c r="AN1" s="119"/>
+      <c r="AO1" s="119"/>
+      <c r="AP1" s="119"/>
+      <c r="AQ1" s="119"/>
+      <c r="AR1" s="119"/>
+      <c r="AS1" s="119"/>
+      <c r="AT1" s="119"/>
+      <c r="AU1" s="120"/>
+      <c r="AV1" s="119"/>
+      <c r="AW1" s="119"/>
+      <c r="AX1" s="119"/>
+      <c r="AY1" s="119"/>
+      <c r="AZ1" s="119"/>
+      <c r="BA1" s="119"/>
+      <c r="BB1" s="119"/>
+      <c r="BC1" s="119"/>
+      <c r="BD1" s="119"/>
+      <c r="BE1" s="119"/>
+      <c r="BF1" s="119"/>
+      <c r="BG1" s="119"/>
+      <c r="BH1" s="119"/>
+      <c r="BI1" s="119"/>
+      <c r="BJ1" s="119"/>
+      <c r="BK1" s="119"/>
+      <c r="BL1" s="119"/>
+      <c r="BM1" s="119"/>
+      <c r="BN1" s="119"/>
+      <c r="BO1" s="119"/>
+      <c r="BP1" s="119"/>
+      <c r="BQ1" s="119"/>
+      <c r="BR1" s="119"/>
+      <c r="BS1" s="119"/>
+      <c r="BT1" s="119"/>
+      <c r="BU1" s="119"/>
+      <c r="BV1" s="121"/>
+      <c r="BW1" s="119"/>
+      <c r="BX1" s="119"/>
+      <c r="BY1" s="119"/>
+      <c r="BZ1" s="119"/>
+      <c r="CA1" s="119"/>
+      <c r="CB1" s="119"/>
+      <c r="CC1" s="119"/>
+      <c r="CD1" s="119"/>
+      <c r="CE1" s="119"/>
+      <c r="CF1" s="119"/>
+      <c r="CG1" s="119"/>
+      <c r="CH1" s="119"/>
+      <c r="CI1" s="119"/>
+      <c r="CJ1" s="119"/>
+      <c r="CK1" s="119"/>
+      <c r="CL1" s="119"/>
+      <c r="CM1" s="119"/>
+      <c r="CN1" s="119"/>
+      <c r="CO1" s="119"/>
+      <c r="CP1" s="119"/>
+      <c r="CQ1" s="119"/>
+      <c r="CR1" s="122"/>
+      <c r="CS1" s="125" t="s">
         <v>2</v>
       </c>
-      <c r="CT1" s="191"/>
-      <c r="CU1" s="191"/>
-      <c r="CV1" s="191"/>
-      <c r="CW1" s="192"/>
+      <c r="CT1" s="126"/>
+      <c r="CU1" s="126"/>
+      <c r="CV1" s="126"/>
+      <c r="CW1" s="127"/>
       <c r="CX1" s="1"/>
-      <c r="CY1" s="180" t="s">
+      <c r="CY1" s="142" t="s">
         <v>3</v>
       </c>
-      <c r="CZ1" s="181"/>
-      <c r="DA1" s="181"/>
-      <c r="DB1" s="181"/>
-      <c r="DC1" s="181"/>
-      <c r="DD1" s="181"/>
-      <c r="DE1" s="181"/>
-      <c r="DF1" s="181"/>
-      <c r="DG1" s="181"/>
+      <c r="CZ1" s="129"/>
+      <c r="DA1" s="129"/>
+      <c r="DB1" s="129"/>
+      <c r="DC1" s="129"/>
+      <c r="DD1" s="129"/>
+      <c r="DE1" s="129"/>
+      <c r="DF1" s="129"/>
+      <c r="DG1" s="129"/>
       <c r="DH1" s="1"/>
       <c r="DI1" s="1"/>
       <c r="DJ1" s="1"/>
@@ -4562,122 +4562,122 @@
       <c r="DW1" s="1"/>
     </row>
     <row r="2" spans="1:129" ht="16.5">
-      <c r="A2" s="124"/>
-      <c r="B2" s="126"/>
-      <c r="C2" s="124"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="126"/>
-      <c r="G2" s="159" t="s">
+      <c r="A2" s="192"/>
+      <c r="B2" s="193"/>
+      <c r="C2" s="192"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="193"/>
+      <c r="G2" s="170" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="119"/>
-      <c r="I2" s="119"/>
-      <c r="J2" s="119"/>
-      <c r="K2" s="119"/>
-      <c r="L2" s="119"/>
-      <c r="M2" s="119"/>
-      <c r="N2" s="119"/>
-      <c r="O2" s="119"/>
-      <c r="P2" s="167"/>
-      <c r="Q2" s="125"/>
-      <c r="R2" s="125"/>
-      <c r="S2" s="125"/>
-      <c r="T2" s="161"/>
-      <c r="U2" s="119"/>
-      <c r="V2" s="119"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="162"/>
-      <c r="Y2" s="119"/>
-      <c r="Z2" s="119"/>
-      <c r="AA2" s="119"/>
-      <c r="AB2" s="137"/>
-      <c r="AC2" s="119"/>
-      <c r="AD2" s="119"/>
-      <c r="AE2" s="119"/>
-      <c r="AF2" s="119"/>
-      <c r="AG2" s="119"/>
-      <c r="AH2" s="119"/>
-      <c r="AI2" s="119"/>
-      <c r="AJ2" s="119"/>
-      <c r="AK2" s="138"/>
-      <c r="AL2" s="162"/>
-      <c r="AM2" s="119"/>
-      <c r="AN2" s="119"/>
-      <c r="AO2" s="119"/>
-      <c r="AP2" s="119"/>
-      <c r="AQ2" s="119"/>
-      <c r="AR2" s="119"/>
-      <c r="AS2" s="119"/>
-      <c r="AT2" s="119"/>
-      <c r="AU2" s="161"/>
-      <c r="AV2" s="119"/>
-      <c r="AW2" s="119"/>
-      <c r="AX2" s="119"/>
-      <c r="AY2" s="119"/>
-      <c r="AZ2" s="119"/>
-      <c r="BA2" s="119"/>
-      <c r="BB2" s="119"/>
-      <c r="BC2" s="119"/>
-      <c r="BD2" s="119"/>
-      <c r="BE2" s="119"/>
-      <c r="BF2" s="119"/>
-      <c r="BG2" s="119"/>
-      <c r="BH2" s="119"/>
-      <c r="BI2" s="119"/>
-      <c r="BJ2" s="119"/>
-      <c r="BK2" s="119"/>
-      <c r="BL2" s="119"/>
-      <c r="BM2" s="119"/>
-      <c r="BN2" s="119"/>
-      <c r="BO2" s="119"/>
-      <c r="BP2" s="119"/>
-      <c r="BQ2" s="119"/>
-      <c r="BR2" s="119"/>
-      <c r="BS2" s="119"/>
-      <c r="BT2" s="119"/>
-      <c r="BU2" s="119"/>
-      <c r="BV2" s="195"/>
-      <c r="BW2" s="119"/>
-      <c r="BX2" s="119"/>
-      <c r="BY2" s="119"/>
-      <c r="BZ2" s="119"/>
-      <c r="CA2" s="119"/>
-      <c r="CB2" s="119"/>
-      <c r="CC2" s="119"/>
-      <c r="CD2" s="119"/>
-      <c r="CE2" s="119"/>
-      <c r="CF2" s="119"/>
-      <c r="CG2" s="119"/>
-      <c r="CH2" s="119"/>
-      <c r="CI2" s="119"/>
-      <c r="CJ2" s="119"/>
-      <c r="CK2" s="119"/>
-      <c r="CL2" s="119"/>
-      <c r="CM2" s="119"/>
-      <c r="CN2" s="119"/>
-      <c r="CO2" s="119"/>
-      <c r="CP2" s="119"/>
-      <c r="CQ2" s="119"/>
-      <c r="CR2" s="138"/>
-      <c r="CS2" s="193"/>
-      <c r="CT2" s="181"/>
-      <c r="CU2" s="181"/>
-      <c r="CV2" s="181"/>
-      <c r="CW2" s="194"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
+      <c r="J2" s="124"/>
+      <c r="K2" s="124"/>
+      <c r="L2" s="124"/>
+      <c r="M2" s="124"/>
+      <c r="N2" s="124"/>
+      <c r="O2" s="124"/>
+      <c r="P2" s="171"/>
+      <c r="Q2" s="172"/>
+      <c r="R2" s="172"/>
+      <c r="S2" s="172"/>
+      <c r="T2" s="134"/>
+      <c r="U2" s="124"/>
+      <c r="V2" s="124"/>
+      <c r="W2" s="136"/>
+      <c r="X2" s="138"/>
+      <c r="Y2" s="124"/>
+      <c r="Z2" s="124"/>
+      <c r="AA2" s="124"/>
+      <c r="AB2" s="180"/>
+      <c r="AC2" s="124"/>
+      <c r="AD2" s="124"/>
+      <c r="AE2" s="124"/>
+      <c r="AF2" s="124"/>
+      <c r="AG2" s="124"/>
+      <c r="AH2" s="124"/>
+      <c r="AI2" s="124"/>
+      <c r="AJ2" s="124"/>
+      <c r="AK2" s="136"/>
+      <c r="AL2" s="138"/>
+      <c r="AM2" s="124"/>
+      <c r="AN2" s="124"/>
+      <c r="AO2" s="124"/>
+      <c r="AP2" s="124"/>
+      <c r="AQ2" s="124"/>
+      <c r="AR2" s="124"/>
+      <c r="AS2" s="124"/>
+      <c r="AT2" s="124"/>
+      <c r="AU2" s="134"/>
+      <c r="AV2" s="124"/>
+      <c r="AW2" s="124"/>
+      <c r="AX2" s="124"/>
+      <c r="AY2" s="124"/>
+      <c r="AZ2" s="124"/>
+      <c r="BA2" s="124"/>
+      <c r="BB2" s="124"/>
+      <c r="BC2" s="124"/>
+      <c r="BD2" s="124"/>
+      <c r="BE2" s="124"/>
+      <c r="BF2" s="124"/>
+      <c r="BG2" s="124"/>
+      <c r="BH2" s="124"/>
+      <c r="BI2" s="124"/>
+      <c r="BJ2" s="124"/>
+      <c r="BK2" s="124"/>
+      <c r="BL2" s="124"/>
+      <c r="BM2" s="124"/>
+      <c r="BN2" s="124"/>
+      <c r="BO2" s="124"/>
+      <c r="BP2" s="124"/>
+      <c r="BQ2" s="124"/>
+      <c r="BR2" s="124"/>
+      <c r="BS2" s="124"/>
+      <c r="BT2" s="124"/>
+      <c r="BU2" s="124"/>
+      <c r="BV2" s="135"/>
+      <c r="BW2" s="124"/>
+      <c r="BX2" s="124"/>
+      <c r="BY2" s="124"/>
+      <c r="BZ2" s="124"/>
+      <c r="CA2" s="124"/>
+      <c r="CB2" s="124"/>
+      <c r="CC2" s="124"/>
+      <c r="CD2" s="124"/>
+      <c r="CE2" s="124"/>
+      <c r="CF2" s="124"/>
+      <c r="CG2" s="124"/>
+      <c r="CH2" s="124"/>
+      <c r="CI2" s="124"/>
+      <c r="CJ2" s="124"/>
+      <c r="CK2" s="124"/>
+      <c r="CL2" s="124"/>
+      <c r="CM2" s="124"/>
+      <c r="CN2" s="124"/>
+      <c r="CO2" s="124"/>
+      <c r="CP2" s="124"/>
+      <c r="CQ2" s="124"/>
+      <c r="CR2" s="136"/>
+      <c r="CS2" s="128"/>
+      <c r="CT2" s="129"/>
+      <c r="CU2" s="129"/>
+      <c r="CV2" s="129"/>
+      <c r="CW2" s="130"/>
       <c r="CX2" s="1"/>
-      <c r="CY2" s="182">
+      <c r="CY2" s="143">
         <f>COUNTA('BASE DE DATOS'!B10:B49)</f>
         <v>25</v>
       </c>
-      <c r="CZ2" s="143"/>
-      <c r="DA2" s="143"/>
-      <c r="DB2" s="143"/>
-      <c r="DC2" s="143"/>
-      <c r="DD2" s="143"/>
-      <c r="DE2" s="143"/>
-      <c r="DF2" s="143"/>
-      <c r="DG2" s="143"/>
+      <c r="CZ2" s="144"/>
+      <c r="DA2" s="144"/>
+      <c r="DB2" s="144"/>
+      <c r="DC2" s="144"/>
+      <c r="DD2" s="144"/>
+      <c r="DE2" s="144"/>
+      <c r="DF2" s="144"/>
+      <c r="DG2" s="144"/>
       <c r="DH2" s="1"/>
       <c r="DI2" s="1"/>
       <c r="DJ2" s="1"/>
@@ -4696,113 +4696,113 @@
       <c r="DW2" s="1"/>
     </row>
     <row r="3" spans="1:129" ht="16.5">
-      <c r="A3" s="118" t="s">
+      <c r="A3" s="173" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="119"/>
-      <c r="C3" s="120"/>
-      <c r="D3" s="156" t="s">
+      <c r="B3" s="124"/>
+      <c r="C3" s="174"/>
+      <c r="D3" s="175" t="s">
         <v>212</v>
       </c>
-      <c r="E3" s="119"/>
-      <c r="F3" s="120"/>
-      <c r="G3" s="140" t="s">
+      <c r="E3" s="124"/>
+      <c r="F3" s="174"/>
+      <c r="G3" s="182" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="119"/>
-      <c r="I3" s="119"/>
-      <c r="J3" s="119"/>
-      <c r="K3" s="119"/>
-      <c r="L3" s="119"/>
-      <c r="M3" s="119"/>
-      <c r="N3" s="119"/>
-      <c r="O3" s="119"/>
-      <c r="P3" s="157"/>
-      <c r="Q3" s="119"/>
-      <c r="R3" s="119"/>
-      <c r="S3" s="119"/>
-      <c r="T3" s="153"/>
-      <c r="U3" s="119"/>
-      <c r="V3" s="119"/>
-      <c r="W3" s="138"/>
-      <c r="X3" s="163"/>
-      <c r="Y3" s="119"/>
-      <c r="Z3" s="119"/>
-      <c r="AA3" s="119"/>
-      <c r="AB3" s="153"/>
-      <c r="AC3" s="119"/>
-      <c r="AD3" s="119"/>
-      <c r="AE3" s="119"/>
-      <c r="AF3" s="119"/>
-      <c r="AG3" s="119"/>
-      <c r="AH3" s="119"/>
-      <c r="AI3" s="119"/>
-      <c r="AJ3" s="119"/>
-      <c r="AK3" s="138"/>
-      <c r="AL3" s="189"/>
-      <c r="AM3" s="119"/>
-      <c r="AN3" s="119"/>
-      <c r="AO3" s="119"/>
-      <c r="AP3" s="119"/>
-      <c r="AQ3" s="119"/>
-      <c r="AR3" s="119"/>
-      <c r="AS3" s="119"/>
-      <c r="AT3" s="119"/>
-      <c r="AU3" s="183"/>
-      <c r="AV3" s="119"/>
-      <c r="AW3" s="119"/>
-      <c r="AX3" s="119"/>
-      <c r="AY3" s="119"/>
-      <c r="AZ3" s="119"/>
-      <c r="BA3" s="119"/>
-      <c r="BB3" s="119"/>
-      <c r="BC3" s="119"/>
-      <c r="BD3" s="119"/>
-      <c r="BE3" s="119"/>
-      <c r="BF3" s="119"/>
-      <c r="BG3" s="119"/>
-      <c r="BH3" s="119"/>
-      <c r="BI3" s="119"/>
-      <c r="BJ3" s="119"/>
-      <c r="BK3" s="119"/>
-      <c r="BL3" s="119"/>
-      <c r="BM3" s="119"/>
-      <c r="BN3" s="119"/>
-      <c r="BO3" s="119"/>
-      <c r="BP3" s="119"/>
-      <c r="BQ3" s="119"/>
-      <c r="BR3" s="119"/>
-      <c r="BS3" s="119"/>
-      <c r="BT3" s="119"/>
-      <c r="BU3" s="119"/>
-      <c r="BV3" s="196"/>
-      <c r="BW3" s="119"/>
-      <c r="BX3" s="119"/>
-      <c r="BY3" s="119"/>
-      <c r="BZ3" s="119"/>
-      <c r="CA3" s="119"/>
-      <c r="CB3" s="119"/>
-      <c r="CC3" s="119"/>
-      <c r="CD3" s="119"/>
-      <c r="CE3" s="119"/>
-      <c r="CF3" s="119"/>
-      <c r="CG3" s="119"/>
-      <c r="CH3" s="119"/>
-      <c r="CI3" s="119"/>
-      <c r="CJ3" s="119"/>
-      <c r="CK3" s="119"/>
-      <c r="CL3" s="119"/>
-      <c r="CM3" s="119"/>
-      <c r="CN3" s="119"/>
-      <c r="CO3" s="119"/>
-      <c r="CP3" s="119"/>
-      <c r="CQ3" s="119"/>
-      <c r="CR3" s="138"/>
-      <c r="CS3" s="193"/>
-      <c r="CT3" s="181"/>
-      <c r="CU3" s="181"/>
-      <c r="CV3" s="181"/>
-      <c r="CW3" s="194"/>
+      <c r="H3" s="124"/>
+      <c r="I3" s="124"/>
+      <c r="J3" s="124"/>
+      <c r="K3" s="124"/>
+      <c r="L3" s="124"/>
+      <c r="M3" s="124"/>
+      <c r="N3" s="124"/>
+      <c r="O3" s="124"/>
+      <c r="P3" s="176"/>
+      <c r="Q3" s="124"/>
+      <c r="R3" s="124"/>
+      <c r="S3" s="124"/>
+      <c r="T3" s="165"/>
+      <c r="U3" s="124"/>
+      <c r="V3" s="124"/>
+      <c r="W3" s="136"/>
+      <c r="X3" s="166"/>
+      <c r="Y3" s="124"/>
+      <c r="Z3" s="124"/>
+      <c r="AA3" s="124"/>
+      <c r="AB3" s="165"/>
+      <c r="AC3" s="124"/>
+      <c r="AD3" s="124"/>
+      <c r="AE3" s="124"/>
+      <c r="AF3" s="124"/>
+      <c r="AG3" s="124"/>
+      <c r="AH3" s="124"/>
+      <c r="AI3" s="124"/>
+      <c r="AJ3" s="124"/>
+      <c r="AK3" s="136"/>
+      <c r="AL3" s="123"/>
+      <c r="AM3" s="124"/>
+      <c r="AN3" s="124"/>
+      <c r="AO3" s="124"/>
+      <c r="AP3" s="124"/>
+      <c r="AQ3" s="124"/>
+      <c r="AR3" s="124"/>
+      <c r="AS3" s="124"/>
+      <c r="AT3" s="124"/>
+      <c r="AU3" s="149"/>
+      <c r="AV3" s="124"/>
+      <c r="AW3" s="124"/>
+      <c r="AX3" s="124"/>
+      <c r="AY3" s="124"/>
+      <c r="AZ3" s="124"/>
+      <c r="BA3" s="124"/>
+      <c r="BB3" s="124"/>
+      <c r="BC3" s="124"/>
+      <c r="BD3" s="124"/>
+      <c r="BE3" s="124"/>
+      <c r="BF3" s="124"/>
+      <c r="BG3" s="124"/>
+      <c r="BH3" s="124"/>
+      <c r="BI3" s="124"/>
+      <c r="BJ3" s="124"/>
+      <c r="BK3" s="124"/>
+      <c r="BL3" s="124"/>
+      <c r="BM3" s="124"/>
+      <c r="BN3" s="124"/>
+      <c r="BO3" s="124"/>
+      <c r="BP3" s="124"/>
+      <c r="BQ3" s="124"/>
+      <c r="BR3" s="124"/>
+      <c r="BS3" s="124"/>
+      <c r="BT3" s="124"/>
+      <c r="BU3" s="124"/>
+      <c r="BV3" s="137"/>
+      <c r="BW3" s="124"/>
+      <c r="BX3" s="124"/>
+      <c r="BY3" s="124"/>
+      <c r="BZ3" s="124"/>
+      <c r="CA3" s="124"/>
+      <c r="CB3" s="124"/>
+      <c r="CC3" s="124"/>
+      <c r="CD3" s="124"/>
+      <c r="CE3" s="124"/>
+      <c r="CF3" s="124"/>
+      <c r="CG3" s="124"/>
+      <c r="CH3" s="124"/>
+      <c r="CI3" s="124"/>
+      <c r="CJ3" s="124"/>
+      <c r="CK3" s="124"/>
+      <c r="CL3" s="124"/>
+      <c r="CM3" s="124"/>
+      <c r="CN3" s="124"/>
+      <c r="CO3" s="124"/>
+      <c r="CP3" s="124"/>
+      <c r="CQ3" s="124"/>
+      <c r="CR3" s="136"/>
+      <c r="CS3" s="128"/>
+      <c r="CT3" s="129"/>
+      <c r="CU3" s="129"/>
+      <c r="CV3" s="129"/>
+      <c r="CW3" s="130"/>
       <c r="CX3" s="1"/>
       <c r="CY3" s="1"/>
       <c r="CZ3" s="1"/>
@@ -4831,142 +4831,142 @@
       <c r="DW3" s="1"/>
     </row>
     <row r="4" spans="1:129" ht="15.75">
-      <c r="A4" s="118" t="s">
+      <c r="A4" s="173" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="119"/>
-      <c r="C4" s="120"/>
-      <c r="D4" s="139" t="s">
+      <c r="B4" s="124"/>
+      <c r="C4" s="174"/>
+      <c r="D4" s="181" t="s">
         <v>211</v>
       </c>
-      <c r="E4" s="119"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="141" t="s">
+      <c r="E4" s="124"/>
+      <c r="F4" s="174"/>
+      <c r="G4" s="183" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="122"/>
-      <c r="I4" s="122"/>
-      <c r="J4" s="122"/>
-      <c r="K4" s="122"/>
-      <c r="L4" s="122"/>
-      <c r="M4" s="122"/>
-      <c r="N4" s="122"/>
-      <c r="O4" s="122"/>
-      <c r="P4" s="144"/>
-      <c r="Q4" s="122"/>
-      <c r="R4" s="122"/>
-      <c r="S4" s="122"/>
-      <c r="T4" s="147"/>
-      <c r="U4" s="122"/>
-      <c r="V4" s="122"/>
-      <c r="W4" s="148"/>
-      <c r="X4" s="150"/>
-      <c r="Y4" s="122"/>
-      <c r="Z4" s="122"/>
-      <c r="AA4" s="122"/>
-      <c r="AB4" s="151"/>
-      <c r="AC4" s="122"/>
-      <c r="AD4" s="122"/>
-      <c r="AE4" s="122"/>
-      <c r="AF4" s="122"/>
-      <c r="AG4" s="122"/>
-      <c r="AH4" s="122"/>
-      <c r="AI4" s="122"/>
-      <c r="AJ4" s="122"/>
-      <c r="AK4" s="148"/>
-      <c r="AL4" s="197"/>
-      <c r="AM4" s="122"/>
-      <c r="AN4" s="122"/>
-      <c r="AO4" s="122"/>
-      <c r="AP4" s="122"/>
-      <c r="AQ4" s="122"/>
-      <c r="AR4" s="122"/>
-      <c r="AS4" s="122"/>
-      <c r="AT4" s="148"/>
-      <c r="AU4" s="184"/>
-      <c r="AV4" s="122"/>
-      <c r="AW4" s="122"/>
-      <c r="AX4" s="122"/>
-      <c r="AY4" s="122"/>
-      <c r="AZ4" s="122"/>
-      <c r="BA4" s="122"/>
-      <c r="BB4" s="122"/>
-      <c r="BC4" s="122"/>
-      <c r="BD4" s="122"/>
-      <c r="BE4" s="122"/>
-      <c r="BF4" s="122"/>
-      <c r="BG4" s="122"/>
-      <c r="BH4" s="122"/>
-      <c r="BI4" s="122"/>
-      <c r="BJ4" s="122"/>
-      <c r="BK4" s="122"/>
-      <c r="BL4" s="122"/>
-      <c r="BM4" s="122"/>
-      <c r="BN4" s="122"/>
-      <c r="BO4" s="122"/>
-      <c r="BP4" s="122"/>
-      <c r="BQ4" s="122"/>
-      <c r="BR4" s="122"/>
-      <c r="BS4" s="122"/>
-      <c r="BT4" s="122"/>
-      <c r="BU4" s="122"/>
-      <c r="BV4" s="185"/>
-      <c r="BW4" s="122"/>
-      <c r="BX4" s="122"/>
-      <c r="BY4" s="122"/>
-      <c r="BZ4" s="122"/>
-      <c r="CA4" s="122"/>
-      <c r="CB4" s="122"/>
-      <c r="CC4" s="122"/>
-      <c r="CD4" s="122"/>
-      <c r="CE4" s="122"/>
-      <c r="CF4" s="122"/>
-      <c r="CG4" s="122"/>
-      <c r="CH4" s="122"/>
-      <c r="CI4" s="122"/>
-      <c r="CJ4" s="122"/>
-      <c r="CK4" s="122"/>
-      <c r="CL4" s="122"/>
-      <c r="CM4" s="122"/>
-      <c r="CN4" s="122"/>
-      <c r="CO4" s="122"/>
-      <c r="CP4" s="122"/>
-      <c r="CQ4" s="122"/>
-      <c r="CR4" s="148"/>
-      <c r="CS4" s="193"/>
-      <c r="CT4" s="181"/>
-      <c r="CU4" s="181"/>
-      <c r="CV4" s="181"/>
-      <c r="CW4" s="194"/>
+      <c r="H4" s="140"/>
+      <c r="I4" s="140"/>
+      <c r="J4" s="140"/>
+      <c r="K4" s="140"/>
+      <c r="L4" s="140"/>
+      <c r="M4" s="140"/>
+      <c r="N4" s="140"/>
+      <c r="O4" s="140"/>
+      <c r="P4" s="185"/>
+      <c r="Q4" s="140"/>
+      <c r="R4" s="140"/>
+      <c r="S4" s="140"/>
+      <c r="T4" s="186"/>
+      <c r="U4" s="140"/>
+      <c r="V4" s="140"/>
+      <c r="W4" s="141"/>
+      <c r="X4" s="187"/>
+      <c r="Y4" s="140"/>
+      <c r="Z4" s="140"/>
+      <c r="AA4" s="140"/>
+      <c r="AB4" s="188"/>
+      <c r="AC4" s="140"/>
+      <c r="AD4" s="140"/>
+      <c r="AE4" s="140"/>
+      <c r="AF4" s="140"/>
+      <c r="AG4" s="140"/>
+      <c r="AH4" s="140"/>
+      <c r="AI4" s="140"/>
+      <c r="AJ4" s="140"/>
+      <c r="AK4" s="141"/>
+      <c r="AL4" s="139"/>
+      <c r="AM4" s="140"/>
+      <c r="AN4" s="140"/>
+      <c r="AO4" s="140"/>
+      <c r="AP4" s="140"/>
+      <c r="AQ4" s="140"/>
+      <c r="AR4" s="140"/>
+      <c r="AS4" s="140"/>
+      <c r="AT4" s="141"/>
+      <c r="AU4" s="150"/>
+      <c r="AV4" s="140"/>
+      <c r="AW4" s="140"/>
+      <c r="AX4" s="140"/>
+      <c r="AY4" s="140"/>
+      <c r="AZ4" s="140"/>
+      <c r="BA4" s="140"/>
+      <c r="BB4" s="140"/>
+      <c r="BC4" s="140"/>
+      <c r="BD4" s="140"/>
+      <c r="BE4" s="140"/>
+      <c r="BF4" s="140"/>
+      <c r="BG4" s="140"/>
+      <c r="BH4" s="140"/>
+      <c r="BI4" s="140"/>
+      <c r="BJ4" s="140"/>
+      <c r="BK4" s="140"/>
+      <c r="BL4" s="140"/>
+      <c r="BM4" s="140"/>
+      <c r="BN4" s="140"/>
+      <c r="BO4" s="140"/>
+      <c r="BP4" s="140"/>
+      <c r="BQ4" s="140"/>
+      <c r="BR4" s="140"/>
+      <c r="BS4" s="140"/>
+      <c r="BT4" s="140"/>
+      <c r="BU4" s="140"/>
+      <c r="BV4" s="151"/>
+      <c r="BW4" s="140"/>
+      <c r="BX4" s="140"/>
+      <c r="BY4" s="140"/>
+      <c r="BZ4" s="140"/>
+      <c r="CA4" s="140"/>
+      <c r="CB4" s="140"/>
+      <c r="CC4" s="140"/>
+      <c r="CD4" s="140"/>
+      <c r="CE4" s="140"/>
+      <c r="CF4" s="140"/>
+      <c r="CG4" s="140"/>
+      <c r="CH4" s="140"/>
+      <c r="CI4" s="140"/>
+      <c r="CJ4" s="140"/>
+      <c r="CK4" s="140"/>
+      <c r="CL4" s="140"/>
+      <c r="CM4" s="140"/>
+      <c r="CN4" s="140"/>
+      <c r="CO4" s="140"/>
+      <c r="CP4" s="140"/>
+      <c r="CQ4" s="140"/>
+      <c r="CR4" s="141"/>
+      <c r="CS4" s="128"/>
+      <c r="CT4" s="129"/>
+      <c r="CU4" s="129"/>
+      <c r="CV4" s="129"/>
+      <c r="CW4" s="130"/>
       <c r="CX4" s="1"/>
-      <c r="CY4" s="171" t="s">
+      <c r="CY4" s="145" t="s">
         <v>9</v>
       </c>
-      <c r="CZ4" s="172"/>
-      <c r="DA4" s="173" t="s">
+      <c r="CZ4" s="146"/>
+      <c r="DA4" s="147" t="s">
         <v>10</v>
       </c>
-      <c r="DB4" s="174"/>
-      <c r="DC4" s="174"/>
-      <c r="DD4" s="174"/>
-      <c r="DE4" s="174"/>
-      <c r="DF4" s="174"/>
-      <c r="DG4" s="172"/>
+      <c r="DB4" s="148"/>
+      <c r="DC4" s="148"/>
+      <c r="DD4" s="148"/>
+      <c r="DE4" s="148"/>
+      <c r="DF4" s="148"/>
+      <c r="DG4" s="146"/>
       <c r="DH4" s="1"/>
       <c r="DI4" s="1"/>
-      <c r="DJ4" s="171" t="s">
+      <c r="DJ4" s="145" t="s">
         <v>11</v>
       </c>
-      <c r="DK4" s="172"/>
-      <c r="DL4" s="173" t="s">
+      <c r="DK4" s="146"/>
+      <c r="DL4" s="147" t="s">
         <v>12</v>
       </c>
-      <c r="DM4" s="174"/>
-      <c r="DN4" s="174"/>
-      <c r="DO4" s="174"/>
-      <c r="DP4" s="174"/>
-      <c r="DQ4" s="174"/>
-      <c r="DR4" s="172"/>
+      <c r="DM4" s="148"/>
+      <c r="DN4" s="148"/>
+      <c r="DO4" s="148"/>
+      <c r="DP4" s="148"/>
+      <c r="DQ4" s="148"/>
+      <c r="DR4" s="146"/>
       <c r="DS4" s="1"/>
       <c r="DT4" s="1"/>
       <c r="DU4" s="1"/>
@@ -4974,112 +4974,112 @@
       <c r="DW4" s="1"/>
     </row>
     <row r="5" spans="1:129" ht="15.75">
-      <c r="A5" s="118" t="s">
+      <c r="A5" s="173" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="119"/>
-      <c r="C5" s="120"/>
-      <c r="D5" s="152" t="str">
+      <c r="B5" s="124"/>
+      <c r="C5" s="174"/>
+      <c r="D5" s="189" t="str">
         <f>'BASE DE DATOS'!C7</f>
         <v>COLEGIO GENERAL SANTANDER</v>
       </c>
-      <c r="E5" s="119"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="142"/>
-      <c r="H5" s="143"/>
-      <c r="I5" s="143"/>
-      <c r="J5" s="143"/>
-      <c r="K5" s="143"/>
-      <c r="L5" s="143"/>
-      <c r="M5" s="143"/>
-      <c r="N5" s="143"/>
-      <c r="O5" s="143"/>
-      <c r="P5" s="145"/>
-      <c r="Q5" s="146"/>
-      <c r="R5" s="146"/>
-      <c r="S5" s="146"/>
-      <c r="T5" s="145"/>
-      <c r="U5" s="146"/>
-      <c r="V5" s="146"/>
-      <c r="W5" s="149"/>
-      <c r="X5" s="145"/>
-      <c r="Y5" s="146"/>
-      <c r="Z5" s="146"/>
-      <c r="AA5" s="146"/>
-      <c r="AB5" s="145"/>
-      <c r="AC5" s="146"/>
-      <c r="AD5" s="146"/>
-      <c r="AE5" s="146"/>
-      <c r="AF5" s="146"/>
-      <c r="AG5" s="146"/>
-      <c r="AH5" s="146"/>
-      <c r="AI5" s="146"/>
-      <c r="AJ5" s="146"/>
-      <c r="AK5" s="149"/>
-      <c r="AL5" s="145"/>
-      <c r="AM5" s="146"/>
-      <c r="AN5" s="146"/>
-      <c r="AO5" s="146"/>
-      <c r="AP5" s="146"/>
-      <c r="AQ5" s="146"/>
-      <c r="AR5" s="146"/>
-      <c r="AS5" s="146"/>
-      <c r="AT5" s="149"/>
-      <c r="AU5" s="145"/>
-      <c r="AV5" s="146"/>
-      <c r="AW5" s="146"/>
-      <c r="AX5" s="146"/>
-      <c r="AY5" s="146"/>
-      <c r="AZ5" s="146"/>
-      <c r="BA5" s="146"/>
-      <c r="BB5" s="146"/>
-      <c r="BC5" s="146"/>
-      <c r="BD5" s="146"/>
-      <c r="BE5" s="146"/>
-      <c r="BF5" s="146"/>
-      <c r="BG5" s="146"/>
-      <c r="BH5" s="146"/>
-      <c r="BI5" s="146"/>
-      <c r="BJ5" s="146"/>
-      <c r="BK5" s="146"/>
-      <c r="BL5" s="146"/>
-      <c r="BM5" s="146"/>
-      <c r="BN5" s="146"/>
-      <c r="BO5" s="146"/>
-      <c r="BP5" s="146"/>
-      <c r="BQ5" s="146"/>
-      <c r="BR5" s="146"/>
-      <c r="BS5" s="146"/>
-      <c r="BT5" s="146"/>
-      <c r="BU5" s="146"/>
-      <c r="BV5" s="145"/>
-      <c r="BW5" s="146"/>
-      <c r="BX5" s="146"/>
-      <c r="BY5" s="146"/>
-      <c r="BZ5" s="146"/>
-      <c r="CA5" s="146"/>
-      <c r="CB5" s="146"/>
-      <c r="CC5" s="146"/>
-      <c r="CD5" s="146"/>
-      <c r="CE5" s="146"/>
-      <c r="CF5" s="146"/>
-      <c r="CG5" s="146"/>
-      <c r="CH5" s="146"/>
-      <c r="CI5" s="146"/>
-      <c r="CJ5" s="146"/>
-      <c r="CK5" s="146"/>
-      <c r="CL5" s="146"/>
-      <c r="CM5" s="146"/>
-      <c r="CN5" s="146"/>
-      <c r="CO5" s="146"/>
-      <c r="CP5" s="146"/>
-      <c r="CQ5" s="146"/>
-      <c r="CR5" s="149"/>
-      <c r="CS5" s="145"/>
-      <c r="CT5" s="146"/>
-      <c r="CU5" s="146"/>
-      <c r="CV5" s="146"/>
-      <c r="CW5" s="149"/>
+      <c r="E5" s="124"/>
+      <c r="F5" s="174"/>
+      <c r="G5" s="184"/>
+      <c r="H5" s="144"/>
+      <c r="I5" s="144"/>
+      <c r="J5" s="144"/>
+      <c r="K5" s="144"/>
+      <c r="L5" s="144"/>
+      <c r="M5" s="144"/>
+      <c r="N5" s="144"/>
+      <c r="O5" s="144"/>
+      <c r="P5" s="131"/>
+      <c r="Q5" s="132"/>
+      <c r="R5" s="132"/>
+      <c r="S5" s="132"/>
+      <c r="T5" s="131"/>
+      <c r="U5" s="132"/>
+      <c r="V5" s="132"/>
+      <c r="W5" s="133"/>
+      <c r="X5" s="131"/>
+      <c r="Y5" s="132"/>
+      <c r="Z5" s="132"/>
+      <c r="AA5" s="132"/>
+      <c r="AB5" s="131"/>
+      <c r="AC5" s="132"/>
+      <c r="AD5" s="132"/>
+      <c r="AE5" s="132"/>
+      <c r="AF5" s="132"/>
+      <c r="AG5" s="132"/>
+      <c r="AH5" s="132"/>
+      <c r="AI5" s="132"/>
+      <c r="AJ5" s="132"/>
+      <c r="AK5" s="133"/>
+      <c r="AL5" s="131"/>
+      <c r="AM5" s="132"/>
+      <c r="AN5" s="132"/>
+      <c r="AO5" s="132"/>
+      <c r="AP5" s="132"/>
+      <c r="AQ5" s="132"/>
+      <c r="AR5" s="132"/>
+      <c r="AS5" s="132"/>
+      <c r="AT5" s="133"/>
+      <c r="AU5" s="131"/>
+      <c r="AV5" s="132"/>
+      <c r="AW5" s="132"/>
+      <c r="AX5" s="132"/>
+      <c r="AY5" s="132"/>
+      <c r="AZ5" s="132"/>
+      <c r="BA5" s="132"/>
+      <c r="BB5" s="132"/>
+      <c r="BC5" s="132"/>
+      <c r="BD5" s="132"/>
+      <c r="BE5" s="132"/>
+      <c r="BF5" s="132"/>
+      <c r="BG5" s="132"/>
+      <c r="BH5" s="132"/>
+      <c r="BI5" s="132"/>
+      <c r="BJ5" s="132"/>
+      <c r="BK5" s="132"/>
+      <c r="BL5" s="132"/>
+      <c r="BM5" s="132"/>
+      <c r="BN5" s="132"/>
+      <c r="BO5" s="132"/>
+      <c r="BP5" s="132"/>
+      <c r="BQ5" s="132"/>
+      <c r="BR5" s="132"/>
+      <c r="BS5" s="132"/>
+      <c r="BT5" s="132"/>
+      <c r="BU5" s="132"/>
+      <c r="BV5" s="131"/>
+      <c r="BW5" s="132"/>
+      <c r="BX5" s="132"/>
+      <c r="BY5" s="132"/>
+      <c r="BZ5" s="132"/>
+      <c r="CA5" s="132"/>
+      <c r="CB5" s="132"/>
+      <c r="CC5" s="132"/>
+      <c r="CD5" s="132"/>
+      <c r="CE5" s="132"/>
+      <c r="CF5" s="132"/>
+      <c r="CG5" s="132"/>
+      <c r="CH5" s="132"/>
+      <c r="CI5" s="132"/>
+      <c r="CJ5" s="132"/>
+      <c r="CK5" s="132"/>
+      <c r="CL5" s="132"/>
+      <c r="CM5" s="132"/>
+      <c r="CN5" s="132"/>
+      <c r="CO5" s="132"/>
+      <c r="CP5" s="132"/>
+      <c r="CQ5" s="132"/>
+      <c r="CR5" s="133"/>
+      <c r="CS5" s="131"/>
+      <c r="CT5" s="132"/>
+      <c r="CU5" s="132"/>
+      <c r="CV5" s="132"/>
+      <c r="CW5" s="133"/>
       <c r="CX5" s="1"/>
       <c r="CY5" s="1"/>
       <c r="CZ5" s="1"/>
@@ -5108,11 +5108,11 @@
       <c r="DW5" s="1"/>
     </row>
     <row r="6" spans="1:129" ht="15.75">
-      <c r="A6" s="118" t="s">
+      <c r="A6" s="173" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="119"/>
-      <c r="C6" s="120"/>
+      <c r="B6" s="124"/>
+      <c r="C6" s="174"/>
       <c r="D6" s="3">
         <f>'BASE DE DATOS'!C4</f>
         <v>3414936</v>
@@ -5124,18 +5124,18 @@
         <f>'BASE DE DATOS'!G7</f>
         <v>10</v>
       </c>
-      <c r="G6" s="121" t="str">
+      <c r="G6" s="195" t="str">
         <f>CY1 &amp; " " &amp; CY2</f>
         <v>TOTAL APRENDICES MATRICULADOS: 25</v>
       </c>
-      <c r="H6" s="122"/>
-      <c r="I6" s="122"/>
-      <c r="J6" s="122"/>
-      <c r="K6" s="122"/>
-      <c r="L6" s="122"/>
-      <c r="M6" s="122"/>
-      <c r="N6" s="122"/>
-      <c r="O6" s="123"/>
+      <c r="H6" s="140"/>
+      <c r="I6" s="140"/>
+      <c r="J6" s="140"/>
+      <c r="K6" s="140"/>
+      <c r="L6" s="140"/>
+      <c r="M6" s="140"/>
+      <c r="N6" s="140"/>
+      <c r="O6" s="191"/>
       <c r="P6" s="6" t="str">
         <f t="shared" ref="P6:CW6" si="0">TEXT(P7,"MMM")</f>
         <v>mar</v>
@@ -5480,41 +5480,41 @@
         <f t="shared" si="0"/>
         <v>dic</v>
       </c>
-      <c r="CX6" s="175" t="s">
+      <c r="CX6" s="152" t="s">
         <v>16</v>
       </c>
-      <c r="CY6" s="176"/>
-      <c r="CZ6" s="176"/>
-      <c r="DA6" s="176"/>
-      <c r="DB6" s="176"/>
-      <c r="DC6" s="176"/>
-      <c r="DD6" s="176"/>
-      <c r="DE6" s="176"/>
-      <c r="DF6" s="176"/>
-      <c r="DG6" s="176"/>
-      <c r="DH6" s="176"/>
-      <c r="DI6" s="176"/>
-      <c r="DJ6" s="176"/>
-      <c r="DK6" s="176"/>
-      <c r="DL6" s="176"/>
-      <c r="DM6" s="176"/>
-      <c r="DN6" s="176"/>
-      <c r="DO6" s="176"/>
-      <c r="DP6" s="176"/>
-      <c r="DQ6" s="176"/>
-      <c r="DR6" s="176"/>
-      <c r="DS6" s="176"/>
-      <c r="DT6" s="176"/>
-      <c r="DU6" s="176"/>
-      <c r="DV6" s="176"/>
-      <c r="DW6" s="176"/>
+      <c r="CY6" s="153"/>
+      <c r="CZ6" s="153"/>
+      <c r="DA6" s="153"/>
+      <c r="DB6" s="153"/>
+      <c r="DC6" s="153"/>
+      <c r="DD6" s="153"/>
+      <c r="DE6" s="153"/>
+      <c r="DF6" s="153"/>
+      <c r="DG6" s="153"/>
+      <c r="DH6" s="153"/>
+      <c r="DI6" s="153"/>
+      <c r="DJ6" s="153"/>
+      <c r="DK6" s="153"/>
+      <c r="DL6" s="153"/>
+      <c r="DM6" s="153"/>
+      <c r="DN6" s="153"/>
+      <c r="DO6" s="153"/>
+      <c r="DP6" s="153"/>
+      <c r="DQ6" s="153"/>
+      <c r="DR6" s="153"/>
+      <c r="DS6" s="153"/>
+      <c r="DT6" s="153"/>
+      <c r="DU6" s="153"/>
+      <c r="DV6" s="153"/>
+      <c r="DW6" s="153"/>
     </row>
     <row r="7" spans="1:129" ht="22.5">
-      <c r="A7" s="127" t="s">
+      <c r="A7" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="119"/>
-      <c r="C7" s="120"/>
+      <c r="B7" s="124"/>
+      <c r="C7" s="174"/>
       <c r="D7" s="8">
         <f>'BASE DE DATOS'!G5</f>
         <v>46084</v>
@@ -5526,15 +5526,15 @@
         <f>'BASE DE DATOS'!G6</f>
         <v>46086</v>
       </c>
-      <c r="G7" s="124"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="125"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="125"/>
-      <c r="L7" s="125"/>
-      <c r="M7" s="125"/>
-      <c r="N7" s="125"/>
-      <c r="O7" s="126"/>
+      <c r="G7" s="192"/>
+      <c r="H7" s="172"/>
+      <c r="I7" s="172"/>
+      <c r="J7" s="172"/>
+      <c r="K7" s="172"/>
+      <c r="L7" s="172"/>
+      <c r="M7" s="172"/>
+      <c r="N7" s="172"/>
+      <c r="O7" s="193"/>
       <c r="P7" s="11">
         <f>D7</f>
         <v>46084</v>
@@ -5879,58 +5879,58 @@
         <f>IF('BASE DE DATOS'!$G$4=1,(CV7+7),IF('BASE DE DATOS'!$G$4=2,(CU7+7)))</f>
         <v>46380</v>
       </c>
-      <c r="CX7" s="177" t="s">
+      <c r="CX7" s="154" t="s">
         <v>19</v>
       </c>
-      <c r="CY7" s="178"/>
-      <c r="CZ7" s="177" t="s">
+      <c r="CY7" s="155"/>
+      <c r="CZ7" s="154" t="s">
         <v>20</v>
       </c>
-      <c r="DA7" s="176"/>
-      <c r="DB7" s="177" t="s">
+      <c r="DA7" s="153"/>
+      <c r="DB7" s="154" t="s">
         <v>21</v>
       </c>
-      <c r="DC7" s="178"/>
-      <c r="DD7" s="177" t="s">
+      <c r="DC7" s="155"/>
+      <c r="DD7" s="154" t="s">
         <v>22</v>
       </c>
-      <c r="DE7" s="178"/>
-      <c r="DF7" s="177" t="s">
+      <c r="DE7" s="155"/>
+      <c r="DF7" s="154" t="s">
         <v>23</v>
       </c>
-      <c r="DG7" s="178"/>
-      <c r="DH7" s="177" t="s">
+      <c r="DG7" s="155"/>
+      <c r="DH7" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="DI7" s="178"/>
-      <c r="DJ7" s="177" t="s">
+      <c r="DI7" s="155"/>
+      <c r="DJ7" s="154" t="s">
         <v>25</v>
       </c>
-      <c r="DK7" s="178"/>
-      <c r="DL7" s="177" t="s">
+      <c r="DK7" s="155"/>
+      <c r="DL7" s="154" t="s">
         <v>26</v>
       </c>
-      <c r="DM7" s="178"/>
-      <c r="DN7" s="177" t="s">
+      <c r="DM7" s="155"/>
+      <c r="DN7" s="154" t="s">
         <v>27</v>
       </c>
-      <c r="DO7" s="178"/>
-      <c r="DP7" s="177" t="s">
+      <c r="DO7" s="155"/>
+      <c r="DP7" s="154" t="s">
         <v>28</v>
       </c>
-      <c r="DQ7" s="178"/>
-      <c r="DR7" s="177" t="s">
+      <c r="DQ7" s="155"/>
+      <c r="DR7" s="154" t="s">
         <v>29</v>
       </c>
-      <c r="DS7" s="178"/>
-      <c r="DT7" s="177" t="s">
+      <c r="DS7" s="155"/>
+      <c r="DT7" s="154" t="s">
         <v>30</v>
       </c>
-      <c r="DU7" s="178"/>
-      <c r="DV7" s="179" t="s">
+      <c r="DU7" s="155"/>
+      <c r="DV7" s="156" t="s">
         <v>31</v>
       </c>
-      <c r="DW7" s="176"/>
+      <c r="DW7" s="153"/>
     </row>
     <row r="8" spans="1:129" ht="30.75" customHeight="1">
       <c r="A8" s="13" t="s">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="G9" s="31">
         <f t="shared" ref="G9:G32" si="3">COUNTIF(P9:CR9,"A")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H9" s="32">
         <f t="shared" ref="H9:H32" si="4">COUNTIF(P9:CR9,"CE")</f>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="O9" s="34">
         <f t="shared" ref="O9:O32" si="11">IFERROR(SUM(H9:K9)/SUM(G9:K9)," ")</f>
-        <v>0.375</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="P9" s="35" t="s">
         <v>38</v>
@@ -6489,7 +6489,9 @@
       </c>
       <c r="X9" s="35"/>
       <c r="Y9" s="35"/>
-      <c r="Z9" s="35"/>
+      <c r="Z9" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA9" s="35"/>
       <c r="AB9" s="35"/>
       <c r="AC9" s="35"/>
@@ -6627,7 +6629,7 @@
       </c>
       <c r="G10" s="41">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H10" s="42">
         <f t="shared" si="4"/>
@@ -6687,7 +6689,9 @@
       </c>
       <c r="X10" s="35"/>
       <c r="Y10" s="35"/>
-      <c r="Z10" s="35"/>
+      <c r="Z10" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA10" s="35"/>
       <c r="AB10" s="35"/>
       <c r="AC10" s="35"/>
@@ -6825,7 +6829,7 @@
       </c>
       <c r="G11" s="41">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" s="42">
         <f t="shared" si="4"/>
@@ -6885,7 +6889,9 @@
       </c>
       <c r="X11" s="35"/>
       <c r="Y11" s="35"/>
-      <c r="Z11" s="35"/>
+      <c r="Z11" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA11" s="35"/>
       <c r="AB11" s="35"/>
       <c r="AC11" s="35"/>
@@ -7023,7 +7029,7 @@
       </c>
       <c r="G12" s="41">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H12" s="42">
         <f t="shared" si="4"/>
@@ -7083,7 +7089,9 @@
       </c>
       <c r="X12" s="35"/>
       <c r="Y12" s="35"/>
-      <c r="Z12" s="35"/>
+      <c r="Z12" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA12" s="35"/>
       <c r="AB12" s="35"/>
       <c r="AC12" s="35"/>
@@ -7221,7 +7229,7 @@
       </c>
       <c r="G13" s="41">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H13" s="42">
         <f t="shared" si="4"/>
@@ -7253,7 +7261,7 @@
       </c>
       <c r="O13" s="43">
         <f t="shared" si="11"/>
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="P13" s="35" t="s">
         <v>38</v>
@@ -7281,7 +7289,9 @@
       </c>
       <c r="X13" s="35"/>
       <c r="Y13" s="35"/>
-      <c r="Z13" s="35"/>
+      <c r="Z13" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA13" s="35"/>
       <c r="AB13" s="35"/>
       <c r="AC13" s="35"/>
@@ -7419,7 +7429,7 @@
       </c>
       <c r="G14" s="41">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H14" s="42">
         <f t="shared" si="4"/>
@@ -7479,7 +7489,9 @@
       </c>
       <c r="X14" s="35"/>
       <c r="Y14" s="35"/>
-      <c r="Z14" s="35"/>
+      <c r="Z14" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA14" s="35"/>
       <c r="AB14" s="35"/>
       <c r="AC14" s="35"/>
@@ -7617,7 +7629,7 @@
       </c>
       <c r="G15" s="41">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H15" s="42">
         <f t="shared" si="4"/>
@@ -7677,7 +7689,9 @@
       </c>
       <c r="X15" s="35"/>
       <c r="Y15" s="35"/>
-      <c r="Z15" s="35"/>
+      <c r="Z15" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA15" s="35"/>
       <c r="AB15" s="35"/>
       <c r="AC15" s="35"/>
@@ -7815,7 +7829,7 @@
       </c>
       <c r="G16" s="41">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H16" s="42">
         <f t="shared" si="4"/>
@@ -7875,7 +7889,9 @@
       </c>
       <c r="X16" s="35"/>
       <c r="Y16" s="35"/>
-      <c r="Z16" s="35"/>
+      <c r="Z16" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA16" s="35"/>
       <c r="AB16" s="35"/>
       <c r="AC16" s="35"/>
@@ -8013,7 +8029,7 @@
       </c>
       <c r="G17" s="41">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H17" s="42">
         <f t="shared" si="4"/>
@@ -8073,7 +8089,9 @@
       </c>
       <c r="X17" s="35"/>
       <c r="Y17" s="35"/>
-      <c r="Z17" s="35"/>
+      <c r="Z17" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA17" s="35"/>
       <c r="AB17" s="35"/>
       <c r="AC17" s="35"/>
@@ -8211,7 +8229,7 @@
       </c>
       <c r="G18" s="41">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H18" s="42">
         <f t="shared" si="4"/>
@@ -8271,7 +8289,9 @@
       </c>
       <c r="X18" s="35"/>
       <c r="Y18" s="35"/>
-      <c r="Z18" s="35"/>
+      <c r="Z18" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA18" s="35"/>
       <c r="AB18" s="35"/>
       <c r="AC18" s="35"/>
@@ -8405,7 +8425,7 @@
       </c>
       <c r="F19" s="30" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>CON FALTAS</v>
       </c>
       <c r="G19" s="41">
         <f t="shared" si="3"/>
@@ -8417,7 +8437,7 @@
       </c>
       <c r="I19" s="42">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="42">
         <f t="shared" si="6"/>
@@ -8441,7 +8461,7 @@
       </c>
       <c r="O19" s="43">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="P19" s="35" t="s">
         <v>38</v>
@@ -8469,7 +8489,9 @@
       </c>
       <c r="X19" s="35"/>
       <c r="Y19" s="35"/>
-      <c r="Z19" s="35"/>
+      <c r="Z19" s="35" t="s">
+        <v>11</v>
+      </c>
       <c r="AA19" s="35"/>
       <c r="AB19" s="35"/>
       <c r="AC19" s="35"/>
@@ -8607,7 +8629,7 @@
       </c>
       <c r="G20" s="41">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H20" s="42">
         <f t="shared" si="4"/>
@@ -8667,7 +8689,9 @@
       </c>
       <c r="X20" s="35"/>
       <c r="Y20" s="35"/>
-      <c r="Z20" s="35"/>
+      <c r="Z20" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA20" s="35"/>
       <c r="AB20" s="35"/>
       <c r="AC20" s="35"/>
@@ -8805,7 +8829,7 @@
       </c>
       <c r="G21" s="41">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H21" s="42">
         <f t="shared" si="4"/>
@@ -8865,7 +8889,9 @@
       </c>
       <c r="X21" s="35"/>
       <c r="Y21" s="35"/>
-      <c r="Z21" s="35"/>
+      <c r="Z21" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA21" s="35"/>
       <c r="AB21" s="35"/>
       <c r="AC21" s="35"/>
@@ -9001,7 +9027,7 @@
       </c>
       <c r="G22" s="41">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H22" s="42">
         <f t="shared" si="4"/>
@@ -9033,7 +9059,7 @@
       </c>
       <c r="O22" s="43">
         <f t="shared" si="11"/>
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="P22" s="35" t="s">
         <v>38</v>
@@ -9061,7 +9087,9 @@
       </c>
       <c r="X22" s="35"/>
       <c r="Y22" s="35"/>
-      <c r="Z22" s="35"/>
+      <c r="Z22" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA22" s="35"/>
       <c r="AB22" s="35"/>
       <c r="AC22" s="35"/>
@@ -9197,7 +9225,7 @@
       </c>
       <c r="G23" s="41">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H23" s="42">
         <f t="shared" si="4"/>
@@ -9229,7 +9257,7 @@
       </c>
       <c r="O23" s="43">
         <f t="shared" si="11"/>
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="P23" s="35" t="s">
         <v>38</v>
@@ -9257,7 +9285,9 @@
       </c>
       <c r="X23" s="35"/>
       <c r="Y23" s="35"/>
-      <c r="Z23" s="35"/>
+      <c r="Z23" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA23" s="35"/>
       <c r="AB23" s="35"/>
       <c r="AC23" s="35"/>
@@ -9393,7 +9423,7 @@
       </c>
       <c r="G24" s="41">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H24" s="42">
         <f t="shared" si="4"/>
@@ -9453,7 +9483,9 @@
       </c>
       <c r="X24" s="35"/>
       <c r="Y24" s="35"/>
-      <c r="Z24" s="35"/>
+      <c r="Z24" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA24" s="35"/>
       <c r="AB24" s="35"/>
       <c r="AC24" s="35"/>
@@ -9589,7 +9621,7 @@
       </c>
       <c r="G25" s="41">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H25" s="42">
         <f t="shared" si="4"/>
@@ -9649,7 +9681,9 @@
       </c>
       <c r="X25" s="35"/>
       <c r="Y25" s="35"/>
-      <c r="Z25" s="35"/>
+      <c r="Z25" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA25" s="35"/>
       <c r="AB25" s="35"/>
       <c r="AC25" s="35"/>
@@ -9785,7 +9819,7 @@
       </c>
       <c r="G26" s="41">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H26" s="42">
         <f t="shared" si="4"/>
@@ -9845,7 +9879,9 @@
       </c>
       <c r="X26" s="35"/>
       <c r="Y26" s="35"/>
-      <c r="Z26" s="35"/>
+      <c r="Z26" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA26" s="35"/>
       <c r="AB26" s="35"/>
       <c r="AC26" s="35"/>
@@ -9981,7 +10017,7 @@
       </c>
       <c r="G27" s="41">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H27" s="42">
         <f t="shared" si="4"/>
@@ -10041,7 +10077,9 @@
       </c>
       <c r="X27" s="35"/>
       <c r="Y27" s="35"/>
-      <c r="Z27" s="35"/>
+      <c r="Z27" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA27" s="35"/>
       <c r="AB27" s="35"/>
       <c r="AC27" s="35"/>
@@ -10177,7 +10215,7 @@
       </c>
       <c r="G28" s="41">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H28" s="42">
         <f t="shared" si="4"/>
@@ -10237,7 +10275,9 @@
       </c>
       <c r="X28" s="35"/>
       <c r="Y28" s="35"/>
-      <c r="Z28" s="35"/>
+      <c r="Z28" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA28" s="35"/>
       <c r="AB28" s="35"/>
       <c r="AC28" s="35"/>
@@ -10373,7 +10413,7 @@
       </c>
       <c r="G29" s="41">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H29" s="42">
         <f t="shared" si="4"/>
@@ -10405,7 +10445,7 @@
       </c>
       <c r="O29" s="43">
         <f t="shared" si="11"/>
-        <v>0.25</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="P29" s="35" t="s">
         <v>38</v>
@@ -10433,7 +10473,9 @@
       </c>
       <c r="X29" s="35"/>
       <c r="Y29" s="35"/>
-      <c r="Z29" s="35"/>
+      <c r="Z29" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA29" s="35"/>
       <c r="AB29" s="35"/>
       <c r="AC29" s="35"/>
@@ -10577,7 +10619,7 @@
       </c>
       <c r="I30" s="42">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="42">
         <f t="shared" si="6"/>
@@ -10601,7 +10643,7 @@
       </c>
       <c r="O30" s="43">
         <f t="shared" si="11"/>
-        <v>0.125</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="P30" s="35" t="s">
         <v>38</v>
@@ -10629,7 +10671,9 @@
       </c>
       <c r="X30" s="35"/>
       <c r="Y30" s="35"/>
-      <c r="Z30" s="35"/>
+      <c r="Z30" s="35" t="s">
+        <v>11</v>
+      </c>
       <c r="AA30" s="35"/>
       <c r="AB30" s="35"/>
       <c r="AC30" s="35"/>
@@ -10765,7 +10809,7 @@
       </c>
       <c r="G31" s="41">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H31" s="42">
         <f t="shared" si="4"/>
@@ -10797,7 +10841,7 @@
       </c>
       <c r="O31" s="43">
         <f t="shared" si="11"/>
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="P31" s="35" t="s">
         <v>38</v>
@@ -10825,7 +10869,9 @@
       </c>
       <c r="X31" s="35"/>
       <c r="Y31" s="35"/>
-      <c r="Z31" s="35"/>
+      <c r="Z31" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA31" s="35"/>
       <c r="AB31" s="35"/>
       <c r="AC31" s="35"/>
@@ -10960,7 +11006,7 @@
       </c>
       <c r="G32" s="41">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H32" s="42">
         <f t="shared" si="4"/>
@@ -10992,7 +11038,7 @@
       </c>
       <c r="O32" s="43">
         <f t="shared" si="11"/>
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="P32" s="35" t="s">
         <v>38</v>
@@ -11020,7 +11066,9 @@
       </c>
       <c r="X32" s="35"/>
       <c r="Y32" s="35"/>
-      <c r="Z32" s="35"/>
+      <c r="Z32" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA32" s="35"/>
       <c r="AB32" s="35"/>
       <c r="AC32" s="35"/>
@@ -11152,7 +11200,7 @@
       <c r="F33" s="30"/>
       <c r="G33" s="41">
         <f t="shared" ref="G33" si="37">COUNTIF(P33:CR33,"A")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H33" s="42">
         <f t="shared" ref="H33" si="38">COUNTIF(P33:CR33,"CE")</f>
@@ -11184,7 +11232,7 @@
       </c>
       <c r="O33" s="43">
         <f t="shared" ref="O33" si="45">IFERROR(SUM(H33:K33)/SUM(G33:K33)," ")</f>
-        <v>0.375</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="P33" s="35" t="s">
         <v>38</v>
@@ -11212,7 +11260,9 @@
       </c>
       <c r="X33" s="35"/>
       <c r="Y33" s="35"/>
-      <c r="Z33" s="35"/>
+      <c r="Z33" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AA33" s="35"/>
       <c r="AB33" s="35"/>
       <c r="AC33" s="35"/>
@@ -11328,20 +11378,20 @@
       <c r="D34" s="82"/>
       <c r="E34" s="82"/>
       <c r="F34" s="81"/>
-      <c r="G34" s="128" t="s">
+      <c r="G34" s="197" t="s">
         <v>59</v>
       </c>
-      <c r="H34" s="129"/>
-      <c r="I34" s="129"/>
-      <c r="J34" s="129"/>
-      <c r="K34" s="129"/>
-      <c r="L34" s="129"/>
-      <c r="M34" s="130"/>
-      <c r="N34" s="131" t="str">
+      <c r="H34" s="158"/>
+      <c r="I34" s="158"/>
+      <c r="J34" s="158"/>
+      <c r="K34" s="158"/>
+      <c r="L34" s="158"/>
+      <c r="M34" s="159"/>
+      <c r="N34" s="160" t="str">
         <f>G8</f>
         <v>A</v>
       </c>
-      <c r="O34" s="132"/>
+      <c r="O34" s="161"/>
       <c r="P34" s="44">
         <f t="shared" ref="P34:AU34" si="47">COUNTIF(P9:P33,"A")</f>
         <v>25</v>
@@ -11384,7 +11434,7 @@
       </c>
       <c r="Z34" s="44">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA34" s="44">
         <f t="shared" si="47"/>
@@ -11726,20 +11776,20 @@
       <c r="D35" s="82"/>
       <c r="E35" s="82"/>
       <c r="F35" s="81"/>
-      <c r="G35" s="164" t="s">
+      <c r="G35" s="167" t="s">
         <v>10</v>
       </c>
-      <c r="H35" s="129"/>
-      <c r="I35" s="129"/>
-      <c r="J35" s="129"/>
-      <c r="K35" s="129"/>
-      <c r="L35" s="129"/>
-      <c r="M35" s="130"/>
-      <c r="N35" s="131" t="str">
+      <c r="H35" s="158"/>
+      <c r="I35" s="158"/>
+      <c r="J35" s="158"/>
+      <c r="K35" s="158"/>
+      <c r="L35" s="158"/>
+      <c r="M35" s="159"/>
+      <c r="N35" s="160" t="str">
         <f>H8</f>
         <v>CE</v>
       </c>
-      <c r="O35" s="132"/>
+      <c r="O35" s="161"/>
       <c r="P35" s="44">
         <f t="shared" ref="P35:AU35" si="51">COUNTIF(P9:P33,"CE")</f>
         <v>0</v>
@@ -12124,20 +12174,20 @@
       <c r="D36" s="82"/>
       <c r="E36" s="82"/>
       <c r="F36" s="81"/>
-      <c r="G36" s="165" t="s">
+      <c r="G36" s="168" t="s">
         <v>12</v>
       </c>
-      <c r="H36" s="129"/>
-      <c r="I36" s="129"/>
-      <c r="J36" s="129"/>
-      <c r="K36" s="129"/>
-      <c r="L36" s="129"/>
-      <c r="M36" s="130"/>
-      <c r="N36" s="131" t="str">
+      <c r="H36" s="158"/>
+      <c r="I36" s="158"/>
+      <c r="J36" s="158"/>
+      <c r="K36" s="158"/>
+      <c r="L36" s="158"/>
+      <c r="M36" s="159"/>
+      <c r="N36" s="160" t="str">
         <f>I8</f>
         <v>SE</v>
       </c>
-      <c r="O36" s="132"/>
+      <c r="O36" s="161"/>
       <c r="P36" s="44">
         <f t="shared" ref="P36:AU36" si="55">COUNTIF(P9:P33,"SE")</f>
         <v>0</v>
@@ -12180,7 +12230,7 @@
       </c>
       <c r="Z36" s="44">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA36" s="44">
         <f t="shared" si="55"/>
@@ -12522,20 +12572,20 @@
       <c r="D37" s="82"/>
       <c r="E37" s="82"/>
       <c r="F37" s="45"/>
-      <c r="G37" s="166" t="s">
+      <c r="G37" s="169" t="s">
         <v>60</v>
       </c>
-      <c r="H37" s="129"/>
-      <c r="I37" s="129"/>
-      <c r="J37" s="129"/>
-      <c r="K37" s="129"/>
-      <c r="L37" s="129"/>
-      <c r="M37" s="130"/>
-      <c r="N37" s="131" t="str">
+      <c r="H37" s="158"/>
+      <c r="I37" s="158"/>
+      <c r="J37" s="158"/>
+      <c r="K37" s="158"/>
+      <c r="L37" s="158"/>
+      <c r="M37" s="159"/>
+      <c r="N37" s="160" t="str">
         <f>J8</f>
         <v>INC</v>
       </c>
-      <c r="O37" s="132"/>
+      <c r="O37" s="161"/>
       <c r="P37" s="44">
         <f t="shared" ref="P37:AU37" si="59">COUNTIF(P9:P33,"INC")</f>
         <v>0</v>
@@ -12920,20 +12970,20 @@
       <c r="D38" s="82"/>
       <c r="E38" s="82"/>
       <c r="F38" s="81"/>
-      <c r="G38" s="160" t="s">
+      <c r="G38" s="164" t="s">
         <v>61</v>
       </c>
-      <c r="H38" s="129"/>
-      <c r="I38" s="129"/>
-      <c r="J38" s="129"/>
-      <c r="K38" s="129"/>
-      <c r="L38" s="129"/>
-      <c r="M38" s="130"/>
-      <c r="N38" s="131" t="str">
+      <c r="H38" s="158"/>
+      <c r="I38" s="158"/>
+      <c r="J38" s="158"/>
+      <c r="K38" s="158"/>
+      <c r="L38" s="158"/>
+      <c r="M38" s="159"/>
+      <c r="N38" s="160" t="str">
         <f>K8</f>
         <v>LIC</v>
       </c>
-      <c r="O38" s="132"/>
+      <c r="O38" s="161"/>
       <c r="P38" s="44">
         <f t="shared" ref="P38:AU38" si="63">COUNTIF(P9:P33,"LIC")</f>
         <v>0</v>
@@ -13318,20 +13368,20 @@
       <c r="D39" s="82"/>
       <c r="E39" s="82"/>
       <c r="F39" s="81"/>
-      <c r="G39" s="168" t="s">
+      <c r="G39" s="157" t="s">
         <v>62</v>
       </c>
-      <c r="H39" s="129"/>
-      <c r="I39" s="129"/>
-      <c r="J39" s="129"/>
-      <c r="K39" s="129"/>
-      <c r="L39" s="129"/>
-      <c r="M39" s="130"/>
-      <c r="N39" s="131" t="str">
+      <c r="H39" s="158"/>
+      <c r="I39" s="158"/>
+      <c r="J39" s="158"/>
+      <c r="K39" s="158"/>
+      <c r="L39" s="158"/>
+      <c r="M39" s="159"/>
+      <c r="N39" s="160" t="str">
         <f>L8</f>
         <v>CLM</v>
       </c>
-      <c r="O39" s="132"/>
+      <c r="O39" s="161"/>
       <c r="P39" s="44">
         <f t="shared" ref="P39:AU39" si="67">COUNTIF(P9:P33,"CLM")</f>
         <v>0</v>
@@ -13716,20 +13766,20 @@
       <c r="D40" s="82"/>
       <c r="E40" s="82"/>
       <c r="F40" s="81"/>
-      <c r="G40" s="169" t="s">
+      <c r="G40" s="162" t="s">
         <v>63</v>
       </c>
-      <c r="H40" s="129"/>
-      <c r="I40" s="129"/>
-      <c r="J40" s="129"/>
-      <c r="K40" s="129"/>
-      <c r="L40" s="129"/>
-      <c r="M40" s="130"/>
-      <c r="N40" s="131" t="str">
+      <c r="H40" s="158"/>
+      <c r="I40" s="158"/>
+      <c r="J40" s="158"/>
+      <c r="K40" s="158"/>
+      <c r="L40" s="158"/>
+      <c r="M40" s="159"/>
+      <c r="N40" s="160" t="str">
         <f>M8</f>
         <v>SFF</v>
       </c>
-      <c r="O40" s="132"/>
+      <c r="O40" s="161"/>
       <c r="P40" s="44">
         <f t="shared" ref="P40:AU40" si="71">COUNTIF(P9:P33,"SFF")</f>
         <v>0</v>
@@ -14114,20 +14164,20 @@
       <c r="D41" s="82"/>
       <c r="E41" s="82"/>
       <c r="F41" s="81"/>
-      <c r="G41" s="170" t="s">
+      <c r="G41" s="163" t="s">
         <v>64</v>
       </c>
-      <c r="H41" s="129"/>
-      <c r="I41" s="129"/>
-      <c r="J41" s="129"/>
-      <c r="K41" s="129"/>
-      <c r="L41" s="129"/>
-      <c r="M41" s="130"/>
-      <c r="N41" s="131" t="str">
+      <c r="H41" s="158"/>
+      <c r="I41" s="158"/>
+      <c r="J41" s="158"/>
+      <c r="K41" s="158"/>
+      <c r="L41" s="158"/>
+      <c r="M41" s="159"/>
+      <c r="N41" s="160" t="str">
         <f>N8</f>
         <v>RET</v>
       </c>
-      <c r="O41" s="132"/>
+      <c r="O41" s="161"/>
       <c r="P41" s="44">
         <f t="shared" ref="P41:AU41" si="75">COUNTIF(P9:P33,"RET")</f>
         <v>0</v>
@@ -39468,23 +39518,53 @@
   </sheetData>
   <autoFilter ref="A8:DW41" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="80">
-    <mergeCell ref="AL1:AT1"/>
-    <mergeCell ref="AU1:BU1"/>
-    <mergeCell ref="BV1:CR1"/>
-    <mergeCell ref="AL3:AT3"/>
-    <mergeCell ref="CS1:CW5"/>
-    <mergeCell ref="AU2:BU2"/>
-    <mergeCell ref="BV2:CR2"/>
-    <mergeCell ref="BV3:CR3"/>
-    <mergeCell ref="AL2:AT2"/>
-    <mergeCell ref="AL4:AT5"/>
-    <mergeCell ref="CY1:DG1"/>
-    <mergeCell ref="CY2:DG2"/>
-    <mergeCell ref="CY4:CZ4"/>
-    <mergeCell ref="DA4:DG4"/>
-    <mergeCell ref="AU3:BU3"/>
-    <mergeCell ref="AU4:BU5"/>
-    <mergeCell ref="BV4:CR5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="G6:O7"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="G34:M34"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="X1:AA1"/>
+    <mergeCell ref="AB1:AK1"/>
+    <mergeCell ref="AB2:AK2"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G3:O3"/>
+    <mergeCell ref="G4:O5"/>
+    <mergeCell ref="P4:S5"/>
+    <mergeCell ref="T4:W5"/>
+    <mergeCell ref="X4:AA5"/>
+    <mergeCell ref="AB4:AK5"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="AB3:AK3"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="P1:S1"/>
+    <mergeCell ref="T1:W1"/>
+    <mergeCell ref="G1:O1"/>
+    <mergeCell ref="G38:M38"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="T2:W2"/>
+    <mergeCell ref="X2:AA2"/>
+    <mergeCell ref="T3:W3"/>
+    <mergeCell ref="X3:AA3"/>
+    <mergeCell ref="N35:O35"/>
+    <mergeCell ref="G35:M35"/>
+    <mergeCell ref="G36:M36"/>
+    <mergeCell ref="N36:O36"/>
+    <mergeCell ref="G37:M37"/>
+    <mergeCell ref="N37:O37"/>
+    <mergeCell ref="G2:O2"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="G39:M39"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="G40:M40"/>
+    <mergeCell ref="N40:O40"/>
+    <mergeCell ref="G41:M41"/>
+    <mergeCell ref="N41:O41"/>
     <mergeCell ref="DJ4:DK4"/>
     <mergeCell ref="DL4:DR4"/>
     <mergeCell ref="CX6:DW6"/>
@@ -39501,53 +39581,23 @@
     <mergeCell ref="DF7:DG7"/>
     <mergeCell ref="DH7:DI7"/>
     <mergeCell ref="DJ7:DK7"/>
-    <mergeCell ref="G39:M39"/>
-    <mergeCell ref="N39:O39"/>
-    <mergeCell ref="G40:M40"/>
-    <mergeCell ref="N40:O40"/>
-    <mergeCell ref="G41:M41"/>
-    <mergeCell ref="N41:O41"/>
-    <mergeCell ref="G38:M38"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="T2:W2"/>
-    <mergeCell ref="X2:AA2"/>
-    <mergeCell ref="T3:W3"/>
-    <mergeCell ref="X3:AA3"/>
-    <mergeCell ref="N35:O35"/>
-    <mergeCell ref="G35:M35"/>
-    <mergeCell ref="G36:M36"/>
-    <mergeCell ref="N36:O36"/>
-    <mergeCell ref="G37:M37"/>
-    <mergeCell ref="N37:O37"/>
-    <mergeCell ref="G2:O2"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="P1:S1"/>
-    <mergeCell ref="T1:W1"/>
-    <mergeCell ref="G1:O1"/>
-    <mergeCell ref="X1:AA1"/>
-    <mergeCell ref="AB1:AK1"/>
-    <mergeCell ref="AB2:AK2"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G3:O3"/>
-    <mergeCell ref="G4:O5"/>
-    <mergeCell ref="P4:S5"/>
-    <mergeCell ref="T4:W5"/>
-    <mergeCell ref="X4:AA5"/>
-    <mergeCell ref="AB4:AK5"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="AB3:AK3"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F2"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="G6:O7"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="G34:M34"/>
-    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="CY1:DG1"/>
+    <mergeCell ref="CY2:DG2"/>
+    <mergeCell ref="CY4:CZ4"/>
+    <mergeCell ref="DA4:DG4"/>
+    <mergeCell ref="AU3:BU3"/>
+    <mergeCell ref="AU4:BU5"/>
+    <mergeCell ref="BV4:CR5"/>
+    <mergeCell ref="AL1:AT1"/>
+    <mergeCell ref="AU1:BU1"/>
+    <mergeCell ref="BV1:CR1"/>
+    <mergeCell ref="AL3:AT3"/>
+    <mergeCell ref="CS1:CW5"/>
+    <mergeCell ref="AU2:BU2"/>
+    <mergeCell ref="BV2:CR2"/>
+    <mergeCell ref="BV3:CR3"/>
+    <mergeCell ref="AL2:AT2"/>
+    <mergeCell ref="AL4:AT5"/>
   </mergeCells>
   <conditionalFormatting sqref="E9:E33">
     <cfRule type="containsText" dxfId="78" priority="1" operator="containsText" text="RETIRADO">
@@ -39913,18 +39963,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A1" s="200">
-        <v>0</v>
-      </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="194"/>
+      <c r="A1" s="204">
+        <v>0</v>
+      </c>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="130"/>
       <c r="L1" s="49"/>
       <c r="M1" s="49"/>
       <c r="N1" s="49"/>
@@ -39942,16 +39992,16 @@
       <c r="Z1" s="49"/>
     </row>
     <row r="2" spans="1:26" ht="15.75">
-      <c r="A2" s="143"/>
-      <c r="B2" s="143"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="194"/>
+      <c r="A2" s="144"/>
+      <c r="B2" s="144"/>
+      <c r="C2" s="144"/>
+      <c r="D2" s="144"/>
+      <c r="E2" s="144"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="144"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="130"/>
       <c r="L2" s="49"/>
       <c r="M2" s="49"/>
       <c r="N2" s="49"/>
@@ -39972,12 +40022,12 @@
       <c r="A3" s="198" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="120"/>
-      <c r="C3" s="201" t="s">
+      <c r="B3" s="174"/>
+      <c r="C3" s="205" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="119"/>
-      <c r="E3" s="120"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="174"/>
       <c r="F3" s="50"/>
       <c r="G3" s="50"/>
       <c r="H3" s="51"/>
@@ -40004,12 +40054,12 @@
       <c r="A4" s="198" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="120"/>
-      <c r="C4" s="202">
+      <c r="B4" s="174"/>
+      <c r="C4" s="206">
         <v>3414936</v>
       </c>
-      <c r="D4" s="119"/>
-      <c r="E4" s="120"/>
+      <c r="D4" s="124"/>
+      <c r="E4" s="174"/>
       <c r="F4" s="52" t="s">
         <v>65</v>
       </c>
@@ -40042,12 +40092,12 @@
       <c r="A5" s="198" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="120"/>
-      <c r="C5" s="199" t="s">
+      <c r="B5" s="174"/>
+      <c r="C5" s="203" t="s">
         <v>89</v>
       </c>
-      <c r="D5" s="119"/>
-      <c r="E5" s="120"/>
+      <c r="D5" s="124"/>
+      <c r="E5" s="174"/>
       <c r="F5" s="52" t="s">
         <v>67</v>
       </c>
@@ -40078,12 +40128,12 @@
       <c r="A6" s="198" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="120"/>
-      <c r="C6" s="203" t="s">
+      <c r="B6" s="174"/>
+      <c r="C6" s="199" t="s">
         <v>90</v>
       </c>
-      <c r="D6" s="119"/>
-      <c r="E6" s="120"/>
+      <c r="D6" s="124"/>
+      <c r="E6" s="174"/>
       <c r="F6" s="52" t="s">
         <v>69</v>
       </c>
@@ -40114,12 +40164,12 @@
       <c r="A7" s="198" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="120"/>
-      <c r="C7" s="204" t="s">
+      <c r="B7" s="174"/>
+      <c r="C7" s="200" t="s">
         <v>91</v>
       </c>
-      <c r="D7" s="119"/>
-      <c r="E7" s="120"/>
+      <c r="D7" s="124"/>
+      <c r="E7" s="174"/>
       <c r="F7" s="56" t="s">
         <v>70</v>
       </c>
@@ -40147,17 +40197,17 @@
       <c r="Z7" s="49"/>
     </row>
     <row r="8" spans="1:26" ht="15.75">
-      <c r="A8" s="205" t="s">
+      <c r="A8" s="201" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="120"/>
-      <c r="C8" s="206" t="s">
+      <c r="B8" s="174"/>
+      <c r="C8" s="202" t="s">
         <v>92</v>
       </c>
-      <c r="D8" s="119"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="120"/>
+      <c r="D8" s="124"/>
+      <c r="E8" s="124"/>
+      <c r="F8" s="124"/>
+      <c r="G8" s="174"/>
       <c r="H8" s="51"/>
       <c r="I8" s="51"/>
       <c r="J8" s="49"/>
@@ -50430,12 +50480,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:G8"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="A1:J2"/>
@@ -50443,6 +50487,12 @@
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C4:E4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:G8"/>
   </mergeCells>
   <conditionalFormatting sqref="B46:B1000">
     <cfRule type="expression" dxfId="13" priority="1">
@@ -50616,9 +50666,9 @@
       <c r="A1" s="210" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="181"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
       <c r="E1" s="70"/>
       <c r="F1" s="70"/>
     </row>

--- a/assets/Listados/CGS - 3414936 - 2026.xlsx
+++ b/assets/Listados/CGS - 3414936 - 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos\Documents\Bot_sena_seguimiento\assets\Listados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342094AA-F4F1-484A-A2CB-5462309145DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB57E127-8FF1-41F3-A62A-25D595AB70DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="294">
   <si>
     <r>
       <rPr>
@@ -2816,84 +2816,23 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="41" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -2902,17 +2841,77 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2926,80 +2925,93 @@
     <xf numFmtId="0" fontId="33" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3012,18 +3024,6 @@
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="13" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4425,125 +4425,125 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:129" ht="24.75" customHeight="1">
-      <c r="A1" s="190"/>
-      <c r="B1" s="191"/>
-      <c r="C1" s="194" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="191"/>
-      <c r="G1" s="170" t="s">
+      <c r="A1" s="154"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="155" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="159" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="124"/>
-      <c r="M1" s="124"/>
-      <c r="N1" s="124"/>
-      <c r="O1" s="124"/>
-      <c r="P1" s="177"/>
-      <c r="Q1" s="124"/>
-      <c r="R1" s="124"/>
-      <c r="S1" s="174"/>
-      <c r="T1" s="178"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="179"/>
-      <c r="Y1" s="119"/>
-      <c r="Z1" s="119"/>
-      <c r="AA1" s="119"/>
-      <c r="AB1" s="178"/>
-      <c r="AC1" s="119"/>
-      <c r="AD1" s="119"/>
-      <c r="AE1" s="119"/>
-      <c r="AF1" s="119"/>
-      <c r="AG1" s="119"/>
-      <c r="AH1" s="119"/>
-      <c r="AI1" s="119"/>
-      <c r="AJ1" s="119"/>
-      <c r="AK1" s="122"/>
-      <c r="AL1" s="118"/>
-      <c r="AM1" s="119"/>
-      <c r="AN1" s="119"/>
-      <c r="AO1" s="119"/>
-      <c r="AP1" s="119"/>
-      <c r="AQ1" s="119"/>
-      <c r="AR1" s="119"/>
-      <c r="AS1" s="119"/>
-      <c r="AT1" s="119"/>
-      <c r="AU1" s="120"/>
-      <c r="AV1" s="119"/>
-      <c r="AW1" s="119"/>
-      <c r="AX1" s="119"/>
-      <c r="AY1" s="119"/>
-      <c r="AZ1" s="119"/>
-      <c r="BA1" s="119"/>
-      <c r="BB1" s="119"/>
-      <c r="BC1" s="119"/>
-      <c r="BD1" s="119"/>
-      <c r="BE1" s="119"/>
-      <c r="BF1" s="119"/>
-      <c r="BG1" s="119"/>
-      <c r="BH1" s="119"/>
-      <c r="BI1" s="119"/>
-      <c r="BJ1" s="119"/>
-      <c r="BK1" s="119"/>
-      <c r="BL1" s="119"/>
-      <c r="BM1" s="119"/>
-      <c r="BN1" s="119"/>
-      <c r="BO1" s="119"/>
-      <c r="BP1" s="119"/>
-      <c r="BQ1" s="119"/>
-      <c r="BR1" s="119"/>
-      <c r="BS1" s="119"/>
-      <c r="BT1" s="119"/>
-      <c r="BU1" s="119"/>
-      <c r="BV1" s="121"/>
-      <c r="BW1" s="119"/>
-      <c r="BX1" s="119"/>
-      <c r="BY1" s="119"/>
-      <c r="BZ1" s="119"/>
-      <c r="CA1" s="119"/>
-      <c r="CB1" s="119"/>
-      <c r="CC1" s="119"/>
-      <c r="CD1" s="119"/>
-      <c r="CE1" s="119"/>
-      <c r="CF1" s="119"/>
-      <c r="CG1" s="119"/>
-      <c r="CH1" s="119"/>
-      <c r="CI1" s="119"/>
-      <c r="CJ1" s="119"/>
-      <c r="CK1" s="119"/>
-      <c r="CL1" s="119"/>
-      <c r="CM1" s="119"/>
-      <c r="CN1" s="119"/>
-      <c r="CO1" s="119"/>
-      <c r="CP1" s="119"/>
-      <c r="CQ1" s="119"/>
-      <c r="CR1" s="122"/>
-      <c r="CS1" s="125" t="s">
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="158"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="135"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="133"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="135"/>
+      <c r="AC1" s="134"/>
+      <c r="AD1" s="134"/>
+      <c r="AE1" s="134"/>
+      <c r="AF1" s="134"/>
+      <c r="AG1" s="134"/>
+      <c r="AH1" s="134"/>
+      <c r="AI1" s="134"/>
+      <c r="AJ1" s="134"/>
+      <c r="AK1" s="136"/>
+      <c r="AL1" s="186"/>
+      <c r="AM1" s="134"/>
+      <c r="AN1" s="134"/>
+      <c r="AO1" s="134"/>
+      <c r="AP1" s="134"/>
+      <c r="AQ1" s="134"/>
+      <c r="AR1" s="134"/>
+      <c r="AS1" s="134"/>
+      <c r="AT1" s="134"/>
+      <c r="AU1" s="187"/>
+      <c r="AV1" s="134"/>
+      <c r="AW1" s="134"/>
+      <c r="AX1" s="134"/>
+      <c r="AY1" s="134"/>
+      <c r="AZ1" s="134"/>
+      <c r="BA1" s="134"/>
+      <c r="BB1" s="134"/>
+      <c r="BC1" s="134"/>
+      <c r="BD1" s="134"/>
+      <c r="BE1" s="134"/>
+      <c r="BF1" s="134"/>
+      <c r="BG1" s="134"/>
+      <c r="BH1" s="134"/>
+      <c r="BI1" s="134"/>
+      <c r="BJ1" s="134"/>
+      <c r="BK1" s="134"/>
+      <c r="BL1" s="134"/>
+      <c r="BM1" s="134"/>
+      <c r="BN1" s="134"/>
+      <c r="BO1" s="134"/>
+      <c r="BP1" s="134"/>
+      <c r="BQ1" s="134"/>
+      <c r="BR1" s="134"/>
+      <c r="BS1" s="134"/>
+      <c r="BT1" s="134"/>
+      <c r="BU1" s="134"/>
+      <c r="BV1" s="188"/>
+      <c r="BW1" s="134"/>
+      <c r="BX1" s="134"/>
+      <c r="BY1" s="134"/>
+      <c r="BZ1" s="134"/>
+      <c r="CA1" s="134"/>
+      <c r="CB1" s="134"/>
+      <c r="CC1" s="134"/>
+      <c r="CD1" s="134"/>
+      <c r="CE1" s="134"/>
+      <c r="CF1" s="134"/>
+      <c r="CG1" s="134"/>
+      <c r="CH1" s="134"/>
+      <c r="CI1" s="134"/>
+      <c r="CJ1" s="134"/>
+      <c r="CK1" s="134"/>
+      <c r="CL1" s="134"/>
+      <c r="CM1" s="134"/>
+      <c r="CN1" s="134"/>
+      <c r="CO1" s="134"/>
+      <c r="CP1" s="134"/>
+      <c r="CQ1" s="134"/>
+      <c r="CR1" s="136"/>
+      <c r="CS1" s="190" t="s">
         <v>2</v>
       </c>
-      <c r="CT1" s="126"/>
-      <c r="CU1" s="126"/>
-      <c r="CV1" s="126"/>
-      <c r="CW1" s="127"/>
+      <c r="CT1" s="191"/>
+      <c r="CU1" s="191"/>
+      <c r="CV1" s="191"/>
+      <c r="CW1" s="192"/>
       <c r="CX1" s="1"/>
-      <c r="CY1" s="142" t="s">
+      <c r="CY1" s="180" t="s">
         <v>3</v>
       </c>
-      <c r="CZ1" s="129"/>
-      <c r="DA1" s="129"/>
-      <c r="DB1" s="129"/>
-      <c r="DC1" s="129"/>
-      <c r="DD1" s="129"/>
-      <c r="DE1" s="129"/>
-      <c r="DF1" s="129"/>
-      <c r="DG1" s="129"/>
+      <c r="CZ1" s="181"/>
+      <c r="DA1" s="181"/>
+      <c r="DB1" s="181"/>
+      <c r="DC1" s="181"/>
+      <c r="DD1" s="181"/>
+      <c r="DE1" s="181"/>
+      <c r="DF1" s="181"/>
+      <c r="DG1" s="181"/>
       <c r="DH1" s="1"/>
       <c r="DI1" s="1"/>
       <c r="DJ1" s="1"/>
@@ -4562,122 +4562,122 @@
       <c r="DW1" s="1"/>
     </row>
     <row r="2" spans="1:129" ht="16.5">
-      <c r="A2" s="192"/>
-      <c r="B2" s="193"/>
-      <c r="C2" s="192"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="193"/>
-      <c r="G2" s="170" t="s">
+      <c r="A2" s="124"/>
+      <c r="B2" s="126"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="126"/>
+      <c r="G2" s="159" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="124"/>
-      <c r="L2" s="124"/>
-      <c r="M2" s="124"/>
-      <c r="N2" s="124"/>
-      <c r="O2" s="124"/>
-      <c r="P2" s="171"/>
-      <c r="Q2" s="172"/>
-      <c r="R2" s="172"/>
-      <c r="S2" s="172"/>
-      <c r="T2" s="134"/>
-      <c r="U2" s="124"/>
-      <c r="V2" s="124"/>
-      <c r="W2" s="136"/>
-      <c r="X2" s="138"/>
-      <c r="Y2" s="124"/>
-      <c r="Z2" s="124"/>
-      <c r="AA2" s="124"/>
-      <c r="AB2" s="180"/>
-      <c r="AC2" s="124"/>
-      <c r="AD2" s="124"/>
-      <c r="AE2" s="124"/>
-      <c r="AF2" s="124"/>
-      <c r="AG2" s="124"/>
-      <c r="AH2" s="124"/>
-      <c r="AI2" s="124"/>
-      <c r="AJ2" s="124"/>
-      <c r="AK2" s="136"/>
-      <c r="AL2" s="138"/>
-      <c r="AM2" s="124"/>
-      <c r="AN2" s="124"/>
-      <c r="AO2" s="124"/>
-      <c r="AP2" s="124"/>
-      <c r="AQ2" s="124"/>
-      <c r="AR2" s="124"/>
-      <c r="AS2" s="124"/>
-      <c r="AT2" s="124"/>
-      <c r="AU2" s="134"/>
-      <c r="AV2" s="124"/>
-      <c r="AW2" s="124"/>
-      <c r="AX2" s="124"/>
-      <c r="AY2" s="124"/>
-      <c r="AZ2" s="124"/>
-      <c r="BA2" s="124"/>
-      <c r="BB2" s="124"/>
-      <c r="BC2" s="124"/>
-      <c r="BD2" s="124"/>
-      <c r="BE2" s="124"/>
-      <c r="BF2" s="124"/>
-      <c r="BG2" s="124"/>
-      <c r="BH2" s="124"/>
-      <c r="BI2" s="124"/>
-      <c r="BJ2" s="124"/>
-      <c r="BK2" s="124"/>
-      <c r="BL2" s="124"/>
-      <c r="BM2" s="124"/>
-      <c r="BN2" s="124"/>
-      <c r="BO2" s="124"/>
-      <c r="BP2" s="124"/>
-      <c r="BQ2" s="124"/>
-      <c r="BR2" s="124"/>
-      <c r="BS2" s="124"/>
-      <c r="BT2" s="124"/>
-      <c r="BU2" s="124"/>
-      <c r="BV2" s="135"/>
-      <c r="BW2" s="124"/>
-      <c r="BX2" s="124"/>
-      <c r="BY2" s="124"/>
-      <c r="BZ2" s="124"/>
-      <c r="CA2" s="124"/>
-      <c r="CB2" s="124"/>
-      <c r="CC2" s="124"/>
-      <c r="CD2" s="124"/>
-      <c r="CE2" s="124"/>
-      <c r="CF2" s="124"/>
-      <c r="CG2" s="124"/>
-      <c r="CH2" s="124"/>
-      <c r="CI2" s="124"/>
-      <c r="CJ2" s="124"/>
-      <c r="CK2" s="124"/>
-      <c r="CL2" s="124"/>
-      <c r="CM2" s="124"/>
-      <c r="CN2" s="124"/>
-      <c r="CO2" s="124"/>
-      <c r="CP2" s="124"/>
-      <c r="CQ2" s="124"/>
-      <c r="CR2" s="136"/>
-      <c r="CS2" s="128"/>
-      <c r="CT2" s="129"/>
-      <c r="CU2" s="129"/>
-      <c r="CV2" s="129"/>
-      <c r="CW2" s="130"/>
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="119"/>
+      <c r="L2" s="119"/>
+      <c r="M2" s="119"/>
+      <c r="N2" s="119"/>
+      <c r="O2" s="119"/>
+      <c r="P2" s="167"/>
+      <c r="Q2" s="125"/>
+      <c r="R2" s="125"/>
+      <c r="S2" s="125"/>
+      <c r="T2" s="161"/>
+      <c r="U2" s="119"/>
+      <c r="V2" s="119"/>
+      <c r="W2" s="138"/>
+      <c r="X2" s="162"/>
+      <c r="Y2" s="119"/>
+      <c r="Z2" s="119"/>
+      <c r="AA2" s="119"/>
+      <c r="AB2" s="137"/>
+      <c r="AC2" s="119"/>
+      <c r="AD2" s="119"/>
+      <c r="AE2" s="119"/>
+      <c r="AF2" s="119"/>
+      <c r="AG2" s="119"/>
+      <c r="AH2" s="119"/>
+      <c r="AI2" s="119"/>
+      <c r="AJ2" s="119"/>
+      <c r="AK2" s="138"/>
+      <c r="AL2" s="162"/>
+      <c r="AM2" s="119"/>
+      <c r="AN2" s="119"/>
+      <c r="AO2" s="119"/>
+      <c r="AP2" s="119"/>
+      <c r="AQ2" s="119"/>
+      <c r="AR2" s="119"/>
+      <c r="AS2" s="119"/>
+      <c r="AT2" s="119"/>
+      <c r="AU2" s="161"/>
+      <c r="AV2" s="119"/>
+      <c r="AW2" s="119"/>
+      <c r="AX2" s="119"/>
+      <c r="AY2" s="119"/>
+      <c r="AZ2" s="119"/>
+      <c r="BA2" s="119"/>
+      <c r="BB2" s="119"/>
+      <c r="BC2" s="119"/>
+      <c r="BD2" s="119"/>
+      <c r="BE2" s="119"/>
+      <c r="BF2" s="119"/>
+      <c r="BG2" s="119"/>
+      <c r="BH2" s="119"/>
+      <c r="BI2" s="119"/>
+      <c r="BJ2" s="119"/>
+      <c r="BK2" s="119"/>
+      <c r="BL2" s="119"/>
+      <c r="BM2" s="119"/>
+      <c r="BN2" s="119"/>
+      <c r="BO2" s="119"/>
+      <c r="BP2" s="119"/>
+      <c r="BQ2" s="119"/>
+      <c r="BR2" s="119"/>
+      <c r="BS2" s="119"/>
+      <c r="BT2" s="119"/>
+      <c r="BU2" s="119"/>
+      <c r="BV2" s="195"/>
+      <c r="BW2" s="119"/>
+      <c r="BX2" s="119"/>
+      <c r="BY2" s="119"/>
+      <c r="BZ2" s="119"/>
+      <c r="CA2" s="119"/>
+      <c r="CB2" s="119"/>
+      <c r="CC2" s="119"/>
+      <c r="CD2" s="119"/>
+      <c r="CE2" s="119"/>
+      <c r="CF2" s="119"/>
+      <c r="CG2" s="119"/>
+      <c r="CH2" s="119"/>
+      <c r="CI2" s="119"/>
+      <c r="CJ2" s="119"/>
+      <c r="CK2" s="119"/>
+      <c r="CL2" s="119"/>
+      <c r="CM2" s="119"/>
+      <c r="CN2" s="119"/>
+      <c r="CO2" s="119"/>
+      <c r="CP2" s="119"/>
+      <c r="CQ2" s="119"/>
+      <c r="CR2" s="138"/>
+      <c r="CS2" s="193"/>
+      <c r="CT2" s="181"/>
+      <c r="CU2" s="181"/>
+      <c r="CV2" s="181"/>
+      <c r="CW2" s="194"/>
       <c r="CX2" s="1"/>
-      <c r="CY2" s="143">
+      <c r="CY2" s="182">
         <f>COUNTA('BASE DE DATOS'!B10:B49)</f>
         <v>25</v>
       </c>
-      <c r="CZ2" s="144"/>
-      <c r="DA2" s="144"/>
-      <c r="DB2" s="144"/>
-      <c r="DC2" s="144"/>
-      <c r="DD2" s="144"/>
-      <c r="DE2" s="144"/>
-      <c r="DF2" s="144"/>
-      <c r="DG2" s="144"/>
+      <c r="CZ2" s="143"/>
+      <c r="DA2" s="143"/>
+      <c r="DB2" s="143"/>
+      <c r="DC2" s="143"/>
+      <c r="DD2" s="143"/>
+      <c r="DE2" s="143"/>
+      <c r="DF2" s="143"/>
+      <c r="DG2" s="143"/>
       <c r="DH2" s="1"/>
       <c r="DI2" s="1"/>
       <c r="DJ2" s="1"/>
@@ -4696,113 +4696,113 @@
       <c r="DW2" s="1"/>
     </row>
     <row r="3" spans="1:129" ht="16.5">
-      <c r="A3" s="173" t="s">
+      <c r="A3" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="124"/>
-      <c r="C3" s="174"/>
-      <c r="D3" s="175" t="s">
+      <c r="B3" s="119"/>
+      <c r="C3" s="120"/>
+      <c r="D3" s="156" t="s">
         <v>212</v>
       </c>
-      <c r="E3" s="124"/>
-      <c r="F3" s="174"/>
-      <c r="G3" s="182" t="s">
+      <c r="E3" s="119"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="140" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="124"/>
-      <c r="I3" s="124"/>
-      <c r="J3" s="124"/>
-      <c r="K3" s="124"/>
-      <c r="L3" s="124"/>
-      <c r="M3" s="124"/>
-      <c r="N3" s="124"/>
-      <c r="O3" s="124"/>
-      <c r="P3" s="176"/>
-      <c r="Q3" s="124"/>
-      <c r="R3" s="124"/>
-      <c r="S3" s="124"/>
-      <c r="T3" s="165"/>
-      <c r="U3" s="124"/>
-      <c r="V3" s="124"/>
-      <c r="W3" s="136"/>
-      <c r="X3" s="166"/>
-      <c r="Y3" s="124"/>
-      <c r="Z3" s="124"/>
-      <c r="AA3" s="124"/>
-      <c r="AB3" s="165"/>
-      <c r="AC3" s="124"/>
-      <c r="AD3" s="124"/>
-      <c r="AE3" s="124"/>
-      <c r="AF3" s="124"/>
-      <c r="AG3" s="124"/>
-      <c r="AH3" s="124"/>
-      <c r="AI3" s="124"/>
-      <c r="AJ3" s="124"/>
-      <c r="AK3" s="136"/>
-      <c r="AL3" s="123"/>
-      <c r="AM3" s="124"/>
-      <c r="AN3" s="124"/>
-      <c r="AO3" s="124"/>
-      <c r="AP3" s="124"/>
-      <c r="AQ3" s="124"/>
-      <c r="AR3" s="124"/>
-      <c r="AS3" s="124"/>
-      <c r="AT3" s="124"/>
-      <c r="AU3" s="149"/>
-      <c r="AV3" s="124"/>
-      <c r="AW3" s="124"/>
-      <c r="AX3" s="124"/>
-      <c r="AY3" s="124"/>
-      <c r="AZ3" s="124"/>
-      <c r="BA3" s="124"/>
-      <c r="BB3" s="124"/>
-      <c r="BC3" s="124"/>
-      <c r="BD3" s="124"/>
-      <c r="BE3" s="124"/>
-      <c r="BF3" s="124"/>
-      <c r="BG3" s="124"/>
-      <c r="BH3" s="124"/>
-      <c r="BI3" s="124"/>
-      <c r="BJ3" s="124"/>
-      <c r="BK3" s="124"/>
-      <c r="BL3" s="124"/>
-      <c r="BM3" s="124"/>
-      <c r="BN3" s="124"/>
-      <c r="BO3" s="124"/>
-      <c r="BP3" s="124"/>
-      <c r="BQ3" s="124"/>
-      <c r="BR3" s="124"/>
-      <c r="BS3" s="124"/>
-      <c r="BT3" s="124"/>
-      <c r="BU3" s="124"/>
-      <c r="BV3" s="137"/>
-      <c r="BW3" s="124"/>
-      <c r="BX3" s="124"/>
-      <c r="BY3" s="124"/>
-      <c r="BZ3" s="124"/>
-      <c r="CA3" s="124"/>
-      <c r="CB3" s="124"/>
-      <c r="CC3" s="124"/>
-      <c r="CD3" s="124"/>
-      <c r="CE3" s="124"/>
-      <c r="CF3" s="124"/>
-      <c r="CG3" s="124"/>
-      <c r="CH3" s="124"/>
-      <c r="CI3" s="124"/>
-      <c r="CJ3" s="124"/>
-      <c r="CK3" s="124"/>
-      <c r="CL3" s="124"/>
-      <c r="CM3" s="124"/>
-      <c r="CN3" s="124"/>
-      <c r="CO3" s="124"/>
-      <c r="CP3" s="124"/>
-      <c r="CQ3" s="124"/>
-      <c r="CR3" s="136"/>
-      <c r="CS3" s="128"/>
-      <c r="CT3" s="129"/>
-      <c r="CU3" s="129"/>
-      <c r="CV3" s="129"/>
-      <c r="CW3" s="130"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="119"/>
+      <c r="J3" s="119"/>
+      <c r="K3" s="119"/>
+      <c r="L3" s="119"/>
+      <c r="M3" s="119"/>
+      <c r="N3" s="119"/>
+      <c r="O3" s="119"/>
+      <c r="P3" s="157"/>
+      <c r="Q3" s="119"/>
+      <c r="R3" s="119"/>
+      <c r="S3" s="119"/>
+      <c r="T3" s="153"/>
+      <c r="U3" s="119"/>
+      <c r="V3" s="119"/>
+      <c r="W3" s="138"/>
+      <c r="X3" s="163"/>
+      <c r="Y3" s="119"/>
+      <c r="Z3" s="119"/>
+      <c r="AA3" s="119"/>
+      <c r="AB3" s="153"/>
+      <c r="AC3" s="119"/>
+      <c r="AD3" s="119"/>
+      <c r="AE3" s="119"/>
+      <c r="AF3" s="119"/>
+      <c r="AG3" s="119"/>
+      <c r="AH3" s="119"/>
+      <c r="AI3" s="119"/>
+      <c r="AJ3" s="119"/>
+      <c r="AK3" s="138"/>
+      <c r="AL3" s="189"/>
+      <c r="AM3" s="119"/>
+      <c r="AN3" s="119"/>
+      <c r="AO3" s="119"/>
+      <c r="AP3" s="119"/>
+      <c r="AQ3" s="119"/>
+      <c r="AR3" s="119"/>
+      <c r="AS3" s="119"/>
+      <c r="AT3" s="119"/>
+      <c r="AU3" s="183"/>
+      <c r="AV3" s="119"/>
+      <c r="AW3" s="119"/>
+      <c r="AX3" s="119"/>
+      <c r="AY3" s="119"/>
+      <c r="AZ3" s="119"/>
+      <c r="BA3" s="119"/>
+      <c r="BB3" s="119"/>
+      <c r="BC3" s="119"/>
+      <c r="BD3" s="119"/>
+      <c r="BE3" s="119"/>
+      <c r="BF3" s="119"/>
+      <c r="BG3" s="119"/>
+      <c r="BH3" s="119"/>
+      <c r="BI3" s="119"/>
+      <c r="BJ3" s="119"/>
+      <c r="BK3" s="119"/>
+      <c r="BL3" s="119"/>
+      <c r="BM3" s="119"/>
+      <c r="BN3" s="119"/>
+      <c r="BO3" s="119"/>
+      <c r="BP3" s="119"/>
+      <c r="BQ3" s="119"/>
+      <c r="BR3" s="119"/>
+      <c r="BS3" s="119"/>
+      <c r="BT3" s="119"/>
+      <c r="BU3" s="119"/>
+      <c r="BV3" s="196"/>
+      <c r="BW3" s="119"/>
+      <c r="BX3" s="119"/>
+      <c r="BY3" s="119"/>
+      <c r="BZ3" s="119"/>
+      <c r="CA3" s="119"/>
+      <c r="CB3" s="119"/>
+      <c r="CC3" s="119"/>
+      <c r="CD3" s="119"/>
+      <c r="CE3" s="119"/>
+      <c r="CF3" s="119"/>
+      <c r="CG3" s="119"/>
+      <c r="CH3" s="119"/>
+      <c r="CI3" s="119"/>
+      <c r="CJ3" s="119"/>
+      <c r="CK3" s="119"/>
+      <c r="CL3" s="119"/>
+      <c r="CM3" s="119"/>
+      <c r="CN3" s="119"/>
+      <c r="CO3" s="119"/>
+      <c r="CP3" s="119"/>
+      <c r="CQ3" s="119"/>
+      <c r="CR3" s="138"/>
+      <c r="CS3" s="193"/>
+      <c r="CT3" s="181"/>
+      <c r="CU3" s="181"/>
+      <c r="CV3" s="181"/>
+      <c r="CW3" s="194"/>
       <c r="CX3" s="1"/>
       <c r="CY3" s="1"/>
       <c r="CZ3" s="1"/>
@@ -4831,142 +4831,142 @@
       <c r="DW3" s="1"/>
     </row>
     <row r="4" spans="1:129" ht="15.75">
-      <c r="A4" s="173" t="s">
+      <c r="A4" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="124"/>
-      <c r="C4" s="174"/>
-      <c r="D4" s="181" t="s">
+      <c r="B4" s="119"/>
+      <c r="C4" s="120"/>
+      <c r="D4" s="139" t="s">
         <v>211</v>
       </c>
-      <c r="E4" s="124"/>
-      <c r="F4" s="174"/>
-      <c r="G4" s="183" t="s">
+      <c r="E4" s="119"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="140"/>
-      <c r="I4" s="140"/>
-      <c r="J4" s="140"/>
-      <c r="K4" s="140"/>
-      <c r="L4" s="140"/>
-      <c r="M4" s="140"/>
-      <c r="N4" s="140"/>
-      <c r="O4" s="140"/>
-      <c r="P4" s="185"/>
-      <c r="Q4" s="140"/>
-      <c r="R4" s="140"/>
-      <c r="S4" s="140"/>
-      <c r="T4" s="186"/>
-      <c r="U4" s="140"/>
-      <c r="V4" s="140"/>
-      <c r="W4" s="141"/>
-      <c r="X4" s="187"/>
-      <c r="Y4" s="140"/>
-      <c r="Z4" s="140"/>
-      <c r="AA4" s="140"/>
-      <c r="AB4" s="188"/>
-      <c r="AC4" s="140"/>
-      <c r="AD4" s="140"/>
-      <c r="AE4" s="140"/>
-      <c r="AF4" s="140"/>
-      <c r="AG4" s="140"/>
-      <c r="AH4" s="140"/>
-      <c r="AI4" s="140"/>
-      <c r="AJ4" s="140"/>
-      <c r="AK4" s="141"/>
-      <c r="AL4" s="139"/>
-      <c r="AM4" s="140"/>
-      <c r="AN4" s="140"/>
-      <c r="AO4" s="140"/>
-      <c r="AP4" s="140"/>
-      <c r="AQ4" s="140"/>
-      <c r="AR4" s="140"/>
-      <c r="AS4" s="140"/>
-      <c r="AT4" s="141"/>
-      <c r="AU4" s="150"/>
-      <c r="AV4" s="140"/>
-      <c r="AW4" s="140"/>
-      <c r="AX4" s="140"/>
-      <c r="AY4" s="140"/>
-      <c r="AZ4" s="140"/>
-      <c r="BA4" s="140"/>
-      <c r="BB4" s="140"/>
-      <c r="BC4" s="140"/>
-      <c r="BD4" s="140"/>
-      <c r="BE4" s="140"/>
-      <c r="BF4" s="140"/>
-      <c r="BG4" s="140"/>
-      <c r="BH4" s="140"/>
-      <c r="BI4" s="140"/>
-      <c r="BJ4" s="140"/>
-      <c r="BK4" s="140"/>
-      <c r="BL4" s="140"/>
-      <c r="BM4" s="140"/>
-      <c r="BN4" s="140"/>
-      <c r="BO4" s="140"/>
-      <c r="BP4" s="140"/>
-      <c r="BQ4" s="140"/>
-      <c r="BR4" s="140"/>
-      <c r="BS4" s="140"/>
-      <c r="BT4" s="140"/>
-      <c r="BU4" s="140"/>
-      <c r="BV4" s="151"/>
-      <c r="BW4" s="140"/>
-      <c r="BX4" s="140"/>
-      <c r="BY4" s="140"/>
-      <c r="BZ4" s="140"/>
-      <c r="CA4" s="140"/>
-      <c r="CB4" s="140"/>
-      <c r="CC4" s="140"/>
-      <c r="CD4" s="140"/>
-      <c r="CE4" s="140"/>
-      <c r="CF4" s="140"/>
-      <c r="CG4" s="140"/>
-      <c r="CH4" s="140"/>
-      <c r="CI4" s="140"/>
-      <c r="CJ4" s="140"/>
-      <c r="CK4" s="140"/>
-      <c r="CL4" s="140"/>
-      <c r="CM4" s="140"/>
-      <c r="CN4" s="140"/>
-      <c r="CO4" s="140"/>
-      <c r="CP4" s="140"/>
-      <c r="CQ4" s="140"/>
-      <c r="CR4" s="141"/>
-      <c r="CS4" s="128"/>
-      <c r="CT4" s="129"/>
-      <c r="CU4" s="129"/>
-      <c r="CV4" s="129"/>
-      <c r="CW4" s="130"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
+      <c r="M4" s="122"/>
+      <c r="N4" s="122"/>
+      <c r="O4" s="122"/>
+      <c r="P4" s="144"/>
+      <c r="Q4" s="122"/>
+      <c r="R4" s="122"/>
+      <c r="S4" s="122"/>
+      <c r="T4" s="147"/>
+      <c r="U4" s="122"/>
+      <c r="V4" s="122"/>
+      <c r="W4" s="148"/>
+      <c r="X4" s="150"/>
+      <c r="Y4" s="122"/>
+      <c r="Z4" s="122"/>
+      <c r="AA4" s="122"/>
+      <c r="AB4" s="151"/>
+      <c r="AC4" s="122"/>
+      <c r="AD4" s="122"/>
+      <c r="AE4" s="122"/>
+      <c r="AF4" s="122"/>
+      <c r="AG4" s="122"/>
+      <c r="AH4" s="122"/>
+      <c r="AI4" s="122"/>
+      <c r="AJ4" s="122"/>
+      <c r="AK4" s="148"/>
+      <c r="AL4" s="197"/>
+      <c r="AM4" s="122"/>
+      <c r="AN4" s="122"/>
+      <c r="AO4" s="122"/>
+      <c r="AP4" s="122"/>
+      <c r="AQ4" s="122"/>
+      <c r="AR4" s="122"/>
+      <c r="AS4" s="122"/>
+      <c r="AT4" s="148"/>
+      <c r="AU4" s="184"/>
+      <c r="AV4" s="122"/>
+      <c r="AW4" s="122"/>
+      <c r="AX4" s="122"/>
+      <c r="AY4" s="122"/>
+      <c r="AZ4" s="122"/>
+      <c r="BA4" s="122"/>
+      <c r="BB4" s="122"/>
+      <c r="BC4" s="122"/>
+      <c r="BD4" s="122"/>
+      <c r="BE4" s="122"/>
+      <c r="BF4" s="122"/>
+      <c r="BG4" s="122"/>
+      <c r="BH4" s="122"/>
+      <c r="BI4" s="122"/>
+      <c r="BJ4" s="122"/>
+      <c r="BK4" s="122"/>
+      <c r="BL4" s="122"/>
+      <c r="BM4" s="122"/>
+      <c r="BN4" s="122"/>
+      <c r="BO4" s="122"/>
+      <c r="BP4" s="122"/>
+      <c r="BQ4" s="122"/>
+      <c r="BR4" s="122"/>
+      <c r="BS4" s="122"/>
+      <c r="BT4" s="122"/>
+      <c r="BU4" s="122"/>
+      <c r="BV4" s="185"/>
+      <c r="BW4" s="122"/>
+      <c r="BX4" s="122"/>
+      <c r="BY4" s="122"/>
+      <c r="BZ4" s="122"/>
+      <c r="CA4" s="122"/>
+      <c r="CB4" s="122"/>
+      <c r="CC4" s="122"/>
+      <c r="CD4" s="122"/>
+      <c r="CE4" s="122"/>
+      <c r="CF4" s="122"/>
+      <c r="CG4" s="122"/>
+      <c r="CH4" s="122"/>
+      <c r="CI4" s="122"/>
+      <c r="CJ4" s="122"/>
+      <c r="CK4" s="122"/>
+      <c r="CL4" s="122"/>
+      <c r="CM4" s="122"/>
+      <c r="CN4" s="122"/>
+      <c r="CO4" s="122"/>
+      <c r="CP4" s="122"/>
+      <c r="CQ4" s="122"/>
+      <c r="CR4" s="148"/>
+      <c r="CS4" s="193"/>
+      <c r="CT4" s="181"/>
+      <c r="CU4" s="181"/>
+      <c r="CV4" s="181"/>
+      <c r="CW4" s="194"/>
       <c r="CX4" s="1"/>
-      <c r="CY4" s="145" t="s">
+      <c r="CY4" s="171" t="s">
         <v>9</v>
       </c>
-      <c r="CZ4" s="146"/>
-      <c r="DA4" s="147" t="s">
+      <c r="CZ4" s="172"/>
+      <c r="DA4" s="173" t="s">
         <v>10</v>
       </c>
-      <c r="DB4" s="148"/>
-      <c r="DC4" s="148"/>
-      <c r="DD4" s="148"/>
-      <c r="DE4" s="148"/>
-      <c r="DF4" s="148"/>
-      <c r="DG4" s="146"/>
+      <c r="DB4" s="174"/>
+      <c r="DC4" s="174"/>
+      <c r="DD4" s="174"/>
+      <c r="DE4" s="174"/>
+      <c r="DF4" s="174"/>
+      <c r="DG4" s="172"/>
       <c r="DH4" s="1"/>
       <c r="DI4" s="1"/>
-      <c r="DJ4" s="145" t="s">
+      <c r="DJ4" s="171" t="s">
         <v>11</v>
       </c>
-      <c r="DK4" s="146"/>
-      <c r="DL4" s="147" t="s">
+      <c r="DK4" s="172"/>
+      <c r="DL4" s="173" t="s">
         <v>12</v>
       </c>
-      <c r="DM4" s="148"/>
-      <c r="DN4" s="148"/>
-      <c r="DO4" s="148"/>
-      <c r="DP4" s="148"/>
-      <c r="DQ4" s="148"/>
-      <c r="DR4" s="146"/>
+      <c r="DM4" s="174"/>
+      <c r="DN4" s="174"/>
+      <c r="DO4" s="174"/>
+      <c r="DP4" s="174"/>
+      <c r="DQ4" s="174"/>
+      <c r="DR4" s="172"/>
       <c r="DS4" s="1"/>
       <c r="DT4" s="1"/>
       <c r="DU4" s="1"/>
@@ -4974,112 +4974,112 @@
       <c r="DW4" s="1"/>
     </row>
     <row r="5" spans="1:129" ht="15.75">
-      <c r="A5" s="173" t="s">
+      <c r="A5" s="118" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="124"/>
-      <c r="C5" s="174"/>
-      <c r="D5" s="189" t="str">
+      <c r="B5" s="119"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="152" t="str">
         <f>'BASE DE DATOS'!C7</f>
         <v>COLEGIO GENERAL SANTANDER</v>
       </c>
-      <c r="E5" s="124"/>
-      <c r="F5" s="174"/>
-      <c r="G5" s="184"/>
-      <c r="H5" s="144"/>
-      <c r="I5" s="144"/>
-      <c r="J5" s="144"/>
-      <c r="K5" s="144"/>
-      <c r="L5" s="144"/>
-      <c r="M5" s="144"/>
-      <c r="N5" s="144"/>
-      <c r="O5" s="144"/>
-      <c r="P5" s="131"/>
-      <c r="Q5" s="132"/>
-      <c r="R5" s="132"/>
-      <c r="S5" s="132"/>
-      <c r="T5" s="131"/>
-      <c r="U5" s="132"/>
-      <c r="V5" s="132"/>
-      <c r="W5" s="133"/>
-      <c r="X5" s="131"/>
-      <c r="Y5" s="132"/>
-      <c r="Z5" s="132"/>
-      <c r="AA5" s="132"/>
-      <c r="AB5" s="131"/>
-      <c r="AC5" s="132"/>
-      <c r="AD5" s="132"/>
-      <c r="AE5" s="132"/>
-      <c r="AF5" s="132"/>
-      <c r="AG5" s="132"/>
-      <c r="AH5" s="132"/>
-      <c r="AI5" s="132"/>
-      <c r="AJ5" s="132"/>
-      <c r="AK5" s="133"/>
-      <c r="AL5" s="131"/>
-      <c r="AM5" s="132"/>
-      <c r="AN5" s="132"/>
-      <c r="AO5" s="132"/>
-      <c r="AP5" s="132"/>
-      <c r="AQ5" s="132"/>
-      <c r="AR5" s="132"/>
-      <c r="AS5" s="132"/>
-      <c r="AT5" s="133"/>
-      <c r="AU5" s="131"/>
-      <c r="AV5" s="132"/>
-      <c r="AW5" s="132"/>
-      <c r="AX5" s="132"/>
-      <c r="AY5" s="132"/>
-      <c r="AZ5" s="132"/>
-      <c r="BA5" s="132"/>
-      <c r="BB5" s="132"/>
-      <c r="BC5" s="132"/>
-      <c r="BD5" s="132"/>
-      <c r="BE5" s="132"/>
-      <c r="BF5" s="132"/>
-      <c r="BG5" s="132"/>
-      <c r="BH5" s="132"/>
-      <c r="BI5" s="132"/>
-      <c r="BJ5" s="132"/>
-      <c r="BK5" s="132"/>
-      <c r="BL5" s="132"/>
-      <c r="BM5" s="132"/>
-      <c r="BN5" s="132"/>
-      <c r="BO5" s="132"/>
-      <c r="BP5" s="132"/>
-      <c r="BQ5" s="132"/>
-      <c r="BR5" s="132"/>
-      <c r="BS5" s="132"/>
-      <c r="BT5" s="132"/>
-      <c r="BU5" s="132"/>
-      <c r="BV5" s="131"/>
-      <c r="BW5" s="132"/>
-      <c r="BX5" s="132"/>
-      <c r="BY5" s="132"/>
-      <c r="BZ5" s="132"/>
-      <c r="CA5" s="132"/>
-      <c r="CB5" s="132"/>
-      <c r="CC5" s="132"/>
-      <c r="CD5" s="132"/>
-      <c r="CE5" s="132"/>
-      <c r="CF5" s="132"/>
-      <c r="CG5" s="132"/>
-      <c r="CH5" s="132"/>
-      <c r="CI5" s="132"/>
-      <c r="CJ5" s="132"/>
-      <c r="CK5" s="132"/>
-      <c r="CL5" s="132"/>
-      <c r="CM5" s="132"/>
-      <c r="CN5" s="132"/>
-      <c r="CO5" s="132"/>
-      <c r="CP5" s="132"/>
-      <c r="CQ5" s="132"/>
-      <c r="CR5" s="133"/>
-      <c r="CS5" s="131"/>
-      <c r="CT5" s="132"/>
-      <c r="CU5" s="132"/>
-      <c r="CV5" s="132"/>
-      <c r="CW5" s="133"/>
+      <c r="E5" s="119"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="142"/>
+      <c r="H5" s="143"/>
+      <c r="I5" s="143"/>
+      <c r="J5" s="143"/>
+      <c r="K5" s="143"/>
+      <c r="L5" s="143"/>
+      <c r="M5" s="143"/>
+      <c r="N5" s="143"/>
+      <c r="O5" s="143"/>
+      <c r="P5" s="145"/>
+      <c r="Q5" s="146"/>
+      <c r="R5" s="146"/>
+      <c r="S5" s="146"/>
+      <c r="T5" s="145"/>
+      <c r="U5" s="146"/>
+      <c r="V5" s="146"/>
+      <c r="W5" s="149"/>
+      <c r="X5" s="145"/>
+      <c r="Y5" s="146"/>
+      <c r="Z5" s="146"/>
+      <c r="AA5" s="146"/>
+      <c r="AB5" s="145"/>
+      <c r="AC5" s="146"/>
+      <c r="AD5" s="146"/>
+      <c r="AE5" s="146"/>
+      <c r="AF5" s="146"/>
+      <c r="AG5" s="146"/>
+      <c r="AH5" s="146"/>
+      <c r="AI5" s="146"/>
+      <c r="AJ5" s="146"/>
+      <c r="AK5" s="149"/>
+      <c r="AL5" s="145"/>
+      <c r="AM5" s="146"/>
+      <c r="AN5" s="146"/>
+      <c r="AO5" s="146"/>
+      <c r="AP5" s="146"/>
+      <c r="AQ5" s="146"/>
+      <c r="AR5" s="146"/>
+      <c r="AS5" s="146"/>
+      <c r="AT5" s="149"/>
+      <c r="AU5" s="145"/>
+      <c r="AV5" s="146"/>
+      <c r="AW5" s="146"/>
+      <c r="AX5" s="146"/>
+      <c r="AY5" s="146"/>
+      <c r="AZ5" s="146"/>
+      <c r="BA5" s="146"/>
+      <c r="BB5" s="146"/>
+      <c r="BC5" s="146"/>
+      <c r="BD5" s="146"/>
+      <c r="BE5" s="146"/>
+      <c r="BF5" s="146"/>
+      <c r="BG5" s="146"/>
+      <c r="BH5" s="146"/>
+      <c r="BI5" s="146"/>
+      <c r="BJ5" s="146"/>
+      <c r="BK5" s="146"/>
+      <c r="BL5" s="146"/>
+      <c r="BM5" s="146"/>
+      <c r="BN5" s="146"/>
+      <c r="BO5" s="146"/>
+      <c r="BP5" s="146"/>
+      <c r="BQ5" s="146"/>
+      <c r="BR5" s="146"/>
+      <c r="BS5" s="146"/>
+      <c r="BT5" s="146"/>
+      <c r="BU5" s="146"/>
+      <c r="BV5" s="145"/>
+      <c r="BW5" s="146"/>
+      <c r="BX5" s="146"/>
+      <c r="BY5" s="146"/>
+      <c r="BZ5" s="146"/>
+      <c r="CA5" s="146"/>
+      <c r="CB5" s="146"/>
+      <c r="CC5" s="146"/>
+      <c r="CD5" s="146"/>
+      <c r="CE5" s="146"/>
+      <c r="CF5" s="146"/>
+      <c r="CG5" s="146"/>
+      <c r="CH5" s="146"/>
+      <c r="CI5" s="146"/>
+      <c r="CJ5" s="146"/>
+      <c r="CK5" s="146"/>
+      <c r="CL5" s="146"/>
+      <c r="CM5" s="146"/>
+      <c r="CN5" s="146"/>
+      <c r="CO5" s="146"/>
+      <c r="CP5" s="146"/>
+      <c r="CQ5" s="146"/>
+      <c r="CR5" s="149"/>
+      <c r="CS5" s="145"/>
+      <c r="CT5" s="146"/>
+      <c r="CU5" s="146"/>
+      <c r="CV5" s="146"/>
+      <c r="CW5" s="149"/>
       <c r="CX5" s="1"/>
       <c r="CY5" s="1"/>
       <c r="CZ5" s="1"/>
@@ -5108,11 +5108,11 @@
       <c r="DW5" s="1"/>
     </row>
     <row r="6" spans="1:129" ht="15.75">
-      <c r="A6" s="173" t="s">
+      <c r="A6" s="118" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="124"/>
-      <c r="C6" s="174"/>
+      <c r="B6" s="119"/>
+      <c r="C6" s="120"/>
       <c r="D6" s="3">
         <f>'BASE DE DATOS'!C4</f>
         <v>3414936</v>
@@ -5124,18 +5124,18 @@
         <f>'BASE DE DATOS'!G7</f>
         <v>10</v>
       </c>
-      <c r="G6" s="195" t="str">
+      <c r="G6" s="121" t="str">
         <f>CY1 &amp; " " &amp; CY2</f>
         <v>TOTAL APRENDICES MATRICULADOS: 25</v>
       </c>
-      <c r="H6" s="140"/>
-      <c r="I6" s="140"/>
-      <c r="J6" s="140"/>
-      <c r="K6" s="140"/>
-      <c r="L6" s="140"/>
-      <c r="M6" s="140"/>
-      <c r="N6" s="140"/>
-      <c r="O6" s="191"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="122"/>
+      <c r="J6" s="122"/>
+      <c r="K6" s="122"/>
+      <c r="L6" s="122"/>
+      <c r="M6" s="122"/>
+      <c r="N6" s="122"/>
+      <c r="O6" s="123"/>
       <c r="P6" s="6" t="str">
         <f t="shared" ref="P6:CW6" si="0">TEXT(P7,"MMM")</f>
         <v>mar</v>
@@ -5480,41 +5480,41 @@
         <f t="shared" si="0"/>
         <v>dic</v>
       </c>
-      <c r="CX6" s="152" t="s">
+      <c r="CX6" s="175" t="s">
         <v>16</v>
       </c>
-      <c r="CY6" s="153"/>
-      <c r="CZ6" s="153"/>
-      <c r="DA6" s="153"/>
-      <c r="DB6" s="153"/>
-      <c r="DC6" s="153"/>
-      <c r="DD6" s="153"/>
-      <c r="DE6" s="153"/>
-      <c r="DF6" s="153"/>
-      <c r="DG6" s="153"/>
-      <c r="DH6" s="153"/>
-      <c r="DI6" s="153"/>
-      <c r="DJ6" s="153"/>
-      <c r="DK6" s="153"/>
-      <c r="DL6" s="153"/>
-      <c r="DM6" s="153"/>
-      <c r="DN6" s="153"/>
-      <c r="DO6" s="153"/>
-      <c r="DP6" s="153"/>
-      <c r="DQ6" s="153"/>
-      <c r="DR6" s="153"/>
-      <c r="DS6" s="153"/>
-      <c r="DT6" s="153"/>
-      <c r="DU6" s="153"/>
-      <c r="DV6" s="153"/>
-      <c r="DW6" s="153"/>
+      <c r="CY6" s="176"/>
+      <c r="CZ6" s="176"/>
+      <c r="DA6" s="176"/>
+      <c r="DB6" s="176"/>
+      <c r="DC6" s="176"/>
+      <c r="DD6" s="176"/>
+      <c r="DE6" s="176"/>
+      <c r="DF6" s="176"/>
+      <c r="DG6" s="176"/>
+      <c r="DH6" s="176"/>
+      <c r="DI6" s="176"/>
+      <c r="DJ6" s="176"/>
+      <c r="DK6" s="176"/>
+      <c r="DL6" s="176"/>
+      <c r="DM6" s="176"/>
+      <c r="DN6" s="176"/>
+      <c r="DO6" s="176"/>
+      <c r="DP6" s="176"/>
+      <c r="DQ6" s="176"/>
+      <c r="DR6" s="176"/>
+      <c r="DS6" s="176"/>
+      <c r="DT6" s="176"/>
+      <c r="DU6" s="176"/>
+      <c r="DV6" s="176"/>
+      <c r="DW6" s="176"/>
     </row>
     <row r="7" spans="1:129" ht="22.5">
-      <c r="A7" s="196" t="s">
+      <c r="A7" s="127" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="124"/>
-      <c r="C7" s="174"/>
+      <c r="B7" s="119"/>
+      <c r="C7" s="120"/>
       <c r="D7" s="8">
         <f>'BASE DE DATOS'!G5</f>
         <v>46084</v>
@@ -5526,15 +5526,15 @@
         <f>'BASE DE DATOS'!G6</f>
         <v>46086</v>
       </c>
-      <c r="G7" s="192"/>
-      <c r="H7" s="172"/>
-      <c r="I7" s="172"/>
-      <c r="J7" s="172"/>
-      <c r="K7" s="172"/>
-      <c r="L7" s="172"/>
-      <c r="M7" s="172"/>
-      <c r="N7" s="172"/>
-      <c r="O7" s="193"/>
+      <c r="G7" s="124"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="125"/>
+      <c r="L7" s="125"/>
+      <c r="M7" s="125"/>
+      <c r="N7" s="125"/>
+      <c r="O7" s="126"/>
       <c r="P7" s="11">
         <f>D7</f>
         <v>46084</v>
@@ -5879,58 +5879,58 @@
         <f>IF('BASE DE DATOS'!$G$4=1,(CV7+7),IF('BASE DE DATOS'!$G$4=2,(CU7+7)))</f>
         <v>46380</v>
       </c>
-      <c r="CX7" s="154" t="s">
+      <c r="CX7" s="177" t="s">
         <v>19</v>
       </c>
-      <c r="CY7" s="155"/>
-      <c r="CZ7" s="154" t="s">
+      <c r="CY7" s="178"/>
+      <c r="CZ7" s="177" t="s">
         <v>20</v>
       </c>
-      <c r="DA7" s="153"/>
-      <c r="DB7" s="154" t="s">
+      <c r="DA7" s="176"/>
+      <c r="DB7" s="177" t="s">
         <v>21</v>
       </c>
-      <c r="DC7" s="155"/>
-      <c r="DD7" s="154" t="s">
+      <c r="DC7" s="178"/>
+      <c r="DD7" s="177" t="s">
         <v>22</v>
       </c>
-      <c r="DE7" s="155"/>
-      <c r="DF7" s="154" t="s">
+      <c r="DE7" s="178"/>
+      <c r="DF7" s="177" t="s">
         <v>23</v>
       </c>
-      <c r="DG7" s="155"/>
-      <c r="DH7" s="154" t="s">
+      <c r="DG7" s="178"/>
+      <c r="DH7" s="177" t="s">
         <v>24</v>
       </c>
-      <c r="DI7" s="155"/>
-      <c r="DJ7" s="154" t="s">
+      <c r="DI7" s="178"/>
+      <c r="DJ7" s="177" t="s">
         <v>25</v>
       </c>
-      <c r="DK7" s="155"/>
-      <c r="DL7" s="154" t="s">
+      <c r="DK7" s="178"/>
+      <c r="DL7" s="177" t="s">
         <v>26</v>
       </c>
-      <c r="DM7" s="155"/>
-      <c r="DN7" s="154" t="s">
+      <c r="DM7" s="178"/>
+      <c r="DN7" s="177" t="s">
         <v>27</v>
       </c>
-      <c r="DO7" s="155"/>
-      <c r="DP7" s="154" t="s">
+      <c r="DO7" s="178"/>
+      <c r="DP7" s="177" t="s">
         <v>28</v>
       </c>
-      <c r="DQ7" s="155"/>
-      <c r="DR7" s="154" t="s">
+      <c r="DQ7" s="178"/>
+      <c r="DR7" s="177" t="s">
         <v>29</v>
       </c>
-      <c r="DS7" s="155"/>
-      <c r="DT7" s="154" t="s">
+      <c r="DS7" s="178"/>
+      <c r="DT7" s="177" t="s">
         <v>30</v>
       </c>
-      <c r="DU7" s="155"/>
-      <c r="DV7" s="156" t="s">
+      <c r="DU7" s="178"/>
+      <c r="DV7" s="179" t="s">
         <v>31</v>
       </c>
-      <c r="DW7" s="153"/>
+      <c r="DW7" s="176"/>
     </row>
     <row r="8" spans="1:129" ht="30.75" customHeight="1">
       <c r="A8" s="13" t="s">
@@ -6429,11 +6429,11 @@
       </c>
       <c r="G9" s="31">
         <f t="shared" ref="G9:G32" si="3">COUNTIF(P9:CR9,"A")</f>
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H9" s="32">
         <f t="shared" ref="H9:H32" si="4">COUNTIF(P9:CR9,"CE")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" s="32">
         <f t="shared" ref="I9:I32" si="5">COUNTIF(P9:CR9,"SE")</f>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="O9" s="34">
         <f t="shared" ref="O9:O32" si="11">IFERROR(SUM(H9:K9)/SUM(G9:K9)," ")</f>
-        <v>0.33333333333333331</v>
+        <v>0.18181818181818182</v>
       </c>
       <c r="P9" s="35" t="s">
         <v>38</v>
@@ -6487,22 +6487,48 @@
       <c r="W9" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="X9" s="35"/>
-      <c r="Y9" s="35"/>
+      <c r="X9" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y9" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z9" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="AA9" s="35"/>
-      <c r="AB9" s="35"/>
-      <c r="AC9" s="35"/>
-      <c r="AD9" s="35"/>
-      <c r="AE9" s="35"/>
-      <c r="AF9" s="35"/>
-      <c r="AG9" s="35"/>
-      <c r="AH9" s="35"/>
-      <c r="AI9" s="35"/>
-      <c r="AJ9" s="35"/>
-      <c r="AK9" s="35"/>
+      <c r="AA9" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB9" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC9" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD9" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE9" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF9" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG9" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH9" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI9" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ9" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK9" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AL9" s="35"/>
       <c r="AM9" s="35"/>
       <c r="AN9" s="35"/>
@@ -6629,11 +6655,11 @@
       </c>
       <c r="G10" s="41">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H10" s="42">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" s="42">
         <f t="shared" si="5"/>
@@ -6661,7 +6687,7 @@
       </c>
       <c r="O10" s="43">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="P10" s="35" t="s">
         <v>38</v>
@@ -6687,22 +6713,48 @@
       <c r="W10" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="X10" s="35"/>
-      <c r="Y10" s="35"/>
+      <c r="X10" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y10" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z10" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="AA10" s="35"/>
-      <c r="AB10" s="35"/>
-      <c r="AC10" s="35"/>
-      <c r="AD10" s="35"/>
-      <c r="AE10" s="35"/>
-      <c r="AF10" s="35"/>
-      <c r="AG10" s="35"/>
-      <c r="AH10" s="35"/>
-      <c r="AI10" s="35"/>
-      <c r="AJ10" s="35"/>
-      <c r="AK10" s="35"/>
+      <c r="AA10" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB10" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC10" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD10" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE10" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF10" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG10" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH10" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI10" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ10" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK10" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AL10" s="35"/>
       <c r="AM10" s="35"/>
       <c r="AN10" s="35"/>
@@ -6829,7 +6881,7 @@
       </c>
       <c r="G11" s="41">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H11" s="42">
         <f t="shared" si="4"/>
@@ -6887,22 +6939,48 @@
       <c r="W11" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="X11" s="35"/>
-      <c r="Y11" s="35"/>
+      <c r="X11" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y11" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z11" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="AA11" s="35"/>
-      <c r="AB11" s="35"/>
-      <c r="AC11" s="35"/>
-      <c r="AD11" s="35"/>
-      <c r="AE11" s="35"/>
-      <c r="AF11" s="35"/>
-      <c r="AG11" s="35"/>
-      <c r="AH11" s="35"/>
-      <c r="AI11" s="35"/>
-      <c r="AJ11" s="35"/>
-      <c r="AK11" s="35"/>
+      <c r="AA11" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB11" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC11" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD11" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE11" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF11" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG11" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH11" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI11" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ11" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK11" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AL11" s="35"/>
       <c r="AM11" s="35"/>
       <c r="AN11" s="35"/>
@@ -7025,11 +7103,11 @@
       </c>
       <c r="F12" s="30" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>CON FALTAS</v>
       </c>
       <c r="G12" s="41">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H12" s="42">
         <f t="shared" si="4"/>
@@ -7037,7 +7115,7 @@
       </c>
       <c r="I12" s="42">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="42">
         <f t="shared" si="6"/>
@@ -7061,7 +7139,7 @@
       </c>
       <c r="O12" s="43">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>4.5454545454545456E-2</v>
       </c>
       <c r="P12" s="35" t="s">
         <v>38</v>
@@ -7087,22 +7165,48 @@
       <c r="W12" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="X12" s="35"/>
-      <c r="Y12" s="35"/>
+      <c r="X12" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y12" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z12" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="AA12" s="35"/>
-      <c r="AB12" s="35"/>
-      <c r="AC12" s="35"/>
-      <c r="AD12" s="35"/>
-      <c r="AE12" s="35"/>
-      <c r="AF12" s="35"/>
-      <c r="AG12" s="35"/>
-      <c r="AH12" s="35"/>
-      <c r="AI12" s="35"/>
-      <c r="AJ12" s="35"/>
-      <c r="AK12" s="35"/>
+      <c r="AA12" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB12" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC12" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD12" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE12" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF12" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG12" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH12" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI12" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ12" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK12" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AL12" s="35"/>
       <c r="AM12" s="35"/>
       <c r="AN12" s="35"/>
@@ -7229,11 +7333,11 @@
       </c>
       <c r="G13" s="41">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H13" s="42">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I13" s="42">
         <f t="shared" si="5"/>
@@ -7261,7 +7365,7 @@
       </c>
       <c r="O13" s="43">
         <f t="shared" si="11"/>
-        <v>0.1111111111111111</v>
+        <v>0.22727272727272727</v>
       </c>
       <c r="P13" s="35" t="s">
         <v>38</v>
@@ -7287,22 +7391,48 @@
       <c r="W13" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="X13" s="35"/>
-      <c r="Y13" s="35"/>
+      <c r="X13" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y13" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z13" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="AA13" s="35"/>
-      <c r="AB13" s="35"/>
-      <c r="AC13" s="35"/>
-      <c r="AD13" s="35"/>
-      <c r="AE13" s="35"/>
-      <c r="AF13" s="35"/>
-      <c r="AG13" s="35"/>
-      <c r="AH13" s="35"/>
-      <c r="AI13" s="35"/>
-      <c r="AJ13" s="35"/>
-      <c r="AK13" s="35"/>
+      <c r="AA13" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB13" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC13" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD13" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE13" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF13" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG13" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH13" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI13" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ13" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK13" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AL13" s="35"/>
       <c r="AM13" s="35"/>
       <c r="AN13" s="35"/>
@@ -7425,11 +7555,11 @@
       </c>
       <c r="F14" s="30" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>CON FALTAS</v>
       </c>
       <c r="G14" s="41">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H14" s="42">
         <f t="shared" si="4"/>
@@ -7437,7 +7567,7 @@
       </c>
       <c r="I14" s="42">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="42">
         <f t="shared" si="6"/>
@@ -7461,7 +7591,7 @@
       </c>
       <c r="O14" s="43">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>4.5454545454545456E-2</v>
       </c>
       <c r="P14" s="35" t="s">
         <v>38</v>
@@ -7487,22 +7617,48 @@
       <c r="W14" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="X14" s="35"/>
-      <c r="Y14" s="35"/>
+      <c r="X14" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y14" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z14" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="AA14" s="35"/>
-      <c r="AB14" s="35"/>
-      <c r="AC14" s="35"/>
-      <c r="AD14" s="35"/>
-      <c r="AE14" s="35"/>
-      <c r="AF14" s="35"/>
-      <c r="AG14" s="35"/>
-      <c r="AH14" s="35"/>
-      <c r="AI14" s="35"/>
-      <c r="AJ14" s="35"/>
-      <c r="AK14" s="35"/>
+      <c r="AA14" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB14" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC14" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD14" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE14" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF14" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG14" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="AH14" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI14" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ14" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK14" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AL14" s="35"/>
       <c r="AM14" s="35"/>
       <c r="AN14" s="35"/>
@@ -7629,11 +7785,11 @@
       </c>
       <c r="G15" s="41">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H15" s="42">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="42">
         <f t="shared" si="5"/>
@@ -7661,7 +7817,7 @@
       </c>
       <c r="O15" s="43">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>4.5454545454545456E-2</v>
       </c>
       <c r="P15" s="35" t="s">
         <v>38</v>
@@ -7687,22 +7843,48 @@
       <c r="W15" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="X15" s="35"/>
-      <c r="Y15" s="35"/>
+      <c r="X15" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y15" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z15" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="AA15" s="35"/>
-      <c r="AB15" s="35"/>
-      <c r="AC15" s="35"/>
-      <c r="AD15" s="35"/>
-      <c r="AE15" s="35"/>
-      <c r="AF15" s="35"/>
-      <c r="AG15" s="35"/>
-      <c r="AH15" s="35"/>
-      <c r="AI15" s="35"/>
-      <c r="AJ15" s="35"/>
-      <c r="AK15" s="35"/>
+      <c r="AA15" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB15" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC15" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD15" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE15" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF15" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG15" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH15" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI15" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ15" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK15" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AL15" s="35"/>
       <c r="AM15" s="35"/>
       <c r="AN15" s="35"/>
@@ -7825,19 +8007,19 @@
       </c>
       <c r="F16" s="30" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>CON FALTAS</v>
       </c>
       <c r="G16" s="41">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H16" s="42">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="42">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="42">
         <f t="shared" si="6"/>
@@ -7861,7 +8043,7 @@
       </c>
       <c r="O16" s="43">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="P16" s="35" t="s">
         <v>38</v>
@@ -7887,22 +8069,48 @@
       <c r="W16" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="X16" s="35"/>
-      <c r="Y16" s="35"/>
+      <c r="X16" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y16" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z16" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="AA16" s="35"/>
-      <c r="AB16" s="35"/>
-      <c r="AC16" s="35"/>
-      <c r="AD16" s="35"/>
-      <c r="AE16" s="35"/>
-      <c r="AF16" s="35"/>
-      <c r="AG16" s="35"/>
-      <c r="AH16" s="35"/>
-      <c r="AI16" s="35"/>
-      <c r="AJ16" s="35"/>
-      <c r="AK16" s="35"/>
+      <c r="AA16" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB16" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC16" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD16" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE16" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF16" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG16" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH16" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI16" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ16" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK16" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AL16" s="35"/>
       <c r="AM16" s="35"/>
       <c r="AN16" s="35"/>
@@ -8025,11 +8233,11 @@
       </c>
       <c r="F17" s="30" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>REVISAR FALTAS</v>
       </c>
       <c r="G17" s="41">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="H17" s="42">
         <f t="shared" si="4"/>
@@ -8037,7 +8245,7 @@
       </c>
       <c r="I17" s="42">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J17" s="42">
         <f t="shared" si="6"/>
@@ -8061,7 +8269,7 @@
       </c>
       <c r="O17" s="43">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>0.13636363636363635</v>
       </c>
       <c r="P17" s="35" t="s">
         <v>38</v>
@@ -8087,22 +8295,48 @@
       <c r="W17" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="X17" s="35"/>
-      <c r="Y17" s="35"/>
+      <c r="X17" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y17" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z17" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="AA17" s="35"/>
-      <c r="AB17" s="35"/>
-      <c r="AC17" s="35"/>
-      <c r="AD17" s="35"/>
-      <c r="AE17" s="35"/>
-      <c r="AF17" s="35"/>
-      <c r="AG17" s="35"/>
-      <c r="AH17" s="35"/>
-      <c r="AI17" s="35"/>
-      <c r="AJ17" s="35"/>
-      <c r="AK17" s="35"/>
+      <c r="AA17" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB17" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC17" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD17" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE17" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF17" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG17" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="AH17" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI17" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ17" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK17" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AL17" s="35"/>
       <c r="AM17" s="35"/>
       <c r="AN17" s="35"/>
@@ -8229,7 +8463,7 @@
       </c>
       <c r="G18" s="41">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H18" s="42">
         <f t="shared" si="4"/>
@@ -8287,22 +8521,48 @@
       <c r="W18" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="X18" s="35"/>
-      <c r="Y18" s="35"/>
+      <c r="X18" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y18" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z18" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="AA18" s="35"/>
-      <c r="AB18" s="35"/>
-      <c r="AC18" s="35"/>
-      <c r="AD18" s="35"/>
-      <c r="AE18" s="35"/>
-      <c r="AF18" s="35"/>
-      <c r="AG18" s="35"/>
-      <c r="AH18" s="35"/>
-      <c r="AI18" s="35"/>
-      <c r="AJ18" s="35"/>
-      <c r="AK18" s="35"/>
+      <c r="AA18" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB18" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC18" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD18" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE18" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF18" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG18" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH18" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI18" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ18" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK18" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AL18" s="35"/>
       <c r="AM18" s="35"/>
       <c r="AN18" s="35"/>
@@ -8429,11 +8689,11 @@
       </c>
       <c r="G19" s="41">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H19" s="42">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="5"/>
@@ -8461,7 +8721,7 @@
       </c>
       <c r="O19" s="43">
         <f t="shared" si="11"/>
-        <v>0.1111111111111111</v>
+        <v>0.13636363636363635</v>
       </c>
       <c r="P19" s="35" t="s">
         <v>38</v>
@@ -8487,22 +8747,48 @@
       <c r="W19" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="X19" s="35"/>
-      <c r="Y19" s="35"/>
+      <c r="X19" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y19" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z19" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA19" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB19" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC19" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD19" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE19" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF19" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG19" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="AA19" s="35"/>
-      <c r="AB19" s="35"/>
-      <c r="AC19" s="35"/>
-      <c r="AD19" s="35"/>
-      <c r="AE19" s="35"/>
-      <c r="AF19" s="35"/>
-      <c r="AG19" s="35"/>
-      <c r="AH19" s="35"/>
-      <c r="AI19" s="35"/>
-      <c r="AJ19" s="35"/>
-      <c r="AK19" s="35"/>
+      <c r="AH19" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI19" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ19" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK19" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AL19" s="35"/>
       <c r="AM19" s="35"/>
       <c r="AN19" s="35"/>
@@ -8629,7 +8915,7 @@
       </c>
       <c r="G20" s="41">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H20" s="42">
         <f t="shared" si="4"/>
@@ -8687,22 +8973,48 @@
       <c r="W20" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="X20" s="35"/>
-      <c r="Y20" s="35"/>
+      <c r="X20" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y20" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z20" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="AA20" s="35"/>
-      <c r="AB20" s="35"/>
-      <c r="AC20" s="35"/>
-      <c r="AD20" s="35"/>
-      <c r="AE20" s="35"/>
-      <c r="AF20" s="35"/>
-      <c r="AG20" s="35"/>
-      <c r="AH20" s="35"/>
-      <c r="AI20" s="35"/>
-      <c r="AJ20" s="35"/>
-      <c r="AK20" s="35"/>
+      <c r="AA20" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB20" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC20" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD20" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE20" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF20" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG20" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH20" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI20" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ20" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK20" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AL20" s="35"/>
       <c r="AM20" s="35"/>
       <c r="AN20" s="35"/>
@@ -8825,11 +9137,11 @@
       </c>
       <c r="F21" s="30" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>CON FALTAS</v>
       </c>
       <c r="G21" s="41">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H21" s="42">
         <f t="shared" si="4"/>
@@ -8837,7 +9149,7 @@
       </c>
       <c r="I21" s="42">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" s="42">
         <f t="shared" si="6"/>
@@ -8861,7 +9173,7 @@
       </c>
       <c r="O21" s="43">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="P21" s="35" t="s">
         <v>38</v>
@@ -8887,22 +9199,48 @@
       <c r="W21" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="X21" s="35"/>
-      <c r="Y21" s="35"/>
+      <c r="X21" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y21" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z21" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="AA21" s="35"/>
-      <c r="AB21" s="35"/>
-      <c r="AC21" s="35"/>
-      <c r="AD21" s="35"/>
-      <c r="AE21" s="35"/>
-      <c r="AF21" s="35"/>
-      <c r="AG21" s="35"/>
-      <c r="AH21" s="35"/>
-      <c r="AI21" s="35"/>
-      <c r="AJ21" s="35"/>
-      <c r="AK21" s="35"/>
+      <c r="AA21" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB21" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC21" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD21" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE21" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF21" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG21" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH21" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI21" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ21" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK21" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AL21" s="35"/>
       <c r="AM21" s="35"/>
       <c r="AN21" s="35"/>
@@ -9027,11 +9365,11 @@
       </c>
       <c r="G22" s="41">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H22" s="42">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" s="42">
         <f t="shared" si="5"/>
@@ -9059,7 +9397,7 @@
       </c>
       <c r="O22" s="43">
         <f t="shared" si="11"/>
-        <v>0.1111111111111111</v>
+        <v>0.13636363636363635</v>
       </c>
       <c r="P22" s="35" t="s">
         <v>38</v>
@@ -9085,22 +9423,48 @@
       <c r="W22" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="X22" s="35"/>
-      <c r="Y22" s="35"/>
+      <c r="X22" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y22" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z22" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="AA22" s="35"/>
-      <c r="AB22" s="35"/>
-      <c r="AC22" s="35"/>
-      <c r="AD22" s="35"/>
-      <c r="AE22" s="35"/>
-      <c r="AF22" s="35"/>
-      <c r="AG22" s="35"/>
-      <c r="AH22" s="35"/>
-      <c r="AI22" s="35"/>
-      <c r="AJ22" s="35"/>
-      <c r="AK22" s="35"/>
+      <c r="AA22" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB22" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC22" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD22" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE22" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF22" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG22" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH22" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI22" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ22" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK22" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AL22" s="35"/>
       <c r="AM22" s="35"/>
       <c r="AN22" s="35"/>
@@ -9225,7 +9589,7 @@
       </c>
       <c r="G23" s="41">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="H23" s="42">
         <f t="shared" si="4"/>
@@ -9257,7 +9621,7 @@
       </c>
       <c r="O23" s="43">
         <f t="shared" si="11"/>
-        <v>0.1111111111111111</v>
+        <v>4.5454545454545456E-2</v>
       </c>
       <c r="P23" s="35" t="s">
         <v>38</v>
@@ -9283,22 +9647,48 @@
       <c r="W23" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="X23" s="35"/>
-      <c r="Y23" s="35"/>
+      <c r="X23" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y23" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z23" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="AA23" s="35"/>
-      <c r="AB23" s="35"/>
-      <c r="AC23" s="35"/>
-      <c r="AD23" s="35"/>
-      <c r="AE23" s="35"/>
-      <c r="AF23" s="35"/>
-      <c r="AG23" s="35"/>
-      <c r="AH23" s="35"/>
-      <c r="AI23" s="35"/>
-      <c r="AJ23" s="35"/>
-      <c r="AK23" s="35"/>
+      <c r="AA23" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB23" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC23" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD23" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE23" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF23" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG23" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH23" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI23" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ23" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK23" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AL23" s="35"/>
       <c r="AM23" s="35"/>
       <c r="AN23" s="35"/>
@@ -9423,7 +9813,7 @@
       </c>
       <c r="G24" s="41">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H24" s="42">
         <f t="shared" si="4"/>
@@ -9481,22 +9871,48 @@
       <c r="W24" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="X24" s="35"/>
-      <c r="Y24" s="35"/>
+      <c r="X24" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y24" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z24" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="AA24" s="35"/>
-      <c r="AB24" s="35"/>
-      <c r="AC24" s="35"/>
-      <c r="AD24" s="35"/>
-      <c r="AE24" s="35"/>
-      <c r="AF24" s="35"/>
-      <c r="AG24" s="35"/>
-      <c r="AH24" s="35"/>
-      <c r="AI24" s="35"/>
-      <c r="AJ24" s="35"/>
-      <c r="AK24" s="35"/>
+      <c r="AA24" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB24" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC24" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD24" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE24" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF24" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG24" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH24" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI24" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ24" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK24" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AL24" s="35"/>
       <c r="AM24" s="35"/>
       <c r="AN24" s="35"/>
@@ -9621,7 +10037,7 @@
       </c>
       <c r="G25" s="41">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H25" s="42">
         <f t="shared" si="4"/>
@@ -9679,22 +10095,48 @@
       <c r="W25" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="X25" s="35"/>
-      <c r="Y25" s="35"/>
+      <c r="X25" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y25" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z25" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="AA25" s="35"/>
-      <c r="AB25" s="35"/>
-      <c r="AC25" s="35"/>
-      <c r="AD25" s="35"/>
-      <c r="AE25" s="35"/>
-      <c r="AF25" s="35"/>
-      <c r="AG25" s="35"/>
-      <c r="AH25" s="35"/>
-      <c r="AI25" s="35"/>
-      <c r="AJ25" s="35"/>
-      <c r="AK25" s="35"/>
+      <c r="AA25" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB25" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC25" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD25" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE25" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF25" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG25" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH25" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI25" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ25" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK25" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AL25" s="35"/>
       <c r="AM25" s="35"/>
       <c r="AN25" s="35"/>
@@ -9819,11 +10261,11 @@
       </c>
       <c r="G26" s="41">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H26" s="42">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="42">
         <f t="shared" si="5"/>
@@ -9851,7 +10293,7 @@
       </c>
       <c r="O26" s="43">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>4.5454545454545456E-2</v>
       </c>
       <c r="P26" s="35" t="s">
         <v>38</v>
@@ -9877,22 +10319,48 @@
       <c r="W26" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="X26" s="35"/>
-      <c r="Y26" s="35"/>
+      <c r="X26" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y26" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z26" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="AA26" s="35"/>
-      <c r="AB26" s="35"/>
-      <c r="AC26" s="35"/>
-      <c r="AD26" s="35"/>
-      <c r="AE26" s="35"/>
-      <c r="AF26" s="35"/>
-      <c r="AG26" s="35"/>
-      <c r="AH26" s="35"/>
-      <c r="AI26" s="35"/>
-      <c r="AJ26" s="35"/>
-      <c r="AK26" s="35"/>
+      <c r="AA26" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB26" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC26" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD26" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE26" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF26" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG26" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH26" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI26" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ26" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK26" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AL26" s="35"/>
       <c r="AM26" s="35"/>
       <c r="AN26" s="35"/>
@@ -10013,19 +10481,19 @@
       </c>
       <c r="F27" s="30" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>CON FALTAS</v>
       </c>
       <c r="G27" s="41">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H27" s="42">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="42">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="42">
         <f t="shared" si="6"/>
@@ -10049,7 +10517,7 @@
       </c>
       <c r="O27" s="43">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="P27" s="35" t="s">
         <v>38</v>
@@ -10075,22 +10543,48 @@
       <c r="W27" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="X27" s="35"/>
-      <c r="Y27" s="35"/>
+      <c r="X27" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y27" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z27" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="AA27" s="35"/>
-      <c r="AB27" s="35"/>
-      <c r="AC27" s="35"/>
-      <c r="AD27" s="35"/>
-      <c r="AE27" s="35"/>
-      <c r="AF27" s="35"/>
-      <c r="AG27" s="35"/>
-      <c r="AH27" s="35"/>
-      <c r="AI27" s="35"/>
-      <c r="AJ27" s="35"/>
-      <c r="AK27" s="35"/>
+      <c r="AA27" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB27" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC27" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD27" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE27" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF27" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG27" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH27" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI27" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ27" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK27" s="35" t="s">
+        <v>11</v>
+      </c>
       <c r="AL27" s="35"/>
       <c r="AM27" s="35"/>
       <c r="AN27" s="35"/>
@@ -10211,11 +10705,11 @@
       </c>
       <c r="F28" s="30" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>CON FALTAS</v>
       </c>
       <c r="G28" s="41">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H28" s="42">
         <f t="shared" si="4"/>
@@ -10223,7 +10717,7 @@
       </c>
       <c r="I28" s="42">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" s="42">
         <f t="shared" si="6"/>
@@ -10247,7 +10741,7 @@
       </c>
       <c r="O28" s="43">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>4.5454545454545456E-2</v>
       </c>
       <c r="P28" s="35" t="s">
         <v>38</v>
@@ -10273,22 +10767,48 @@
       <c r="W28" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="X28" s="35"/>
-      <c r="Y28" s="35"/>
+      <c r="X28" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y28" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z28" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="AA28" s="35"/>
-      <c r="AB28" s="35"/>
-      <c r="AC28" s="35"/>
-      <c r="AD28" s="35"/>
-      <c r="AE28" s="35"/>
-      <c r="AF28" s="35"/>
-      <c r="AG28" s="35"/>
-      <c r="AH28" s="35"/>
-      <c r="AI28" s="35"/>
-      <c r="AJ28" s="35"/>
-      <c r="AK28" s="35"/>
+      <c r="AA28" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB28" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC28" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD28" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE28" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF28" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG28" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH28" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI28" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ28" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK28" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AL28" s="35"/>
       <c r="AM28" s="35"/>
       <c r="AN28" s="35"/>
@@ -10409,19 +10929,19 @@
       </c>
       <c r="F29" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>CON FALTAS</v>
+        <v>FALTAS INTERMITENTES</v>
       </c>
       <c r="G29" s="41">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H29" s="42">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I29" s="42">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J29" s="42">
         <f t="shared" si="6"/>
@@ -10445,7 +10965,7 @@
       </c>
       <c r="O29" s="43">
         <f t="shared" si="11"/>
-        <v>0.22222222222222221</v>
+        <v>0.45454545454545453</v>
       </c>
       <c r="P29" s="35" t="s">
         <v>38</v>
@@ -10469,24 +10989,50 @@
         <v>38</v>
       </c>
       <c r="W29" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="X29" s="35"/>
-      <c r="Y29" s="35"/>
+        <v>9</v>
+      </c>
+      <c r="X29" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y29" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z29" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="AA29" s="35"/>
-      <c r="AB29" s="35"/>
-      <c r="AC29" s="35"/>
-      <c r="AD29" s="35"/>
-      <c r="AE29" s="35"/>
-      <c r="AF29" s="35"/>
-      <c r="AG29" s="35"/>
-      <c r="AH29" s="35"/>
-      <c r="AI29" s="35"/>
-      <c r="AJ29" s="35"/>
-      <c r="AK29" s="35"/>
+      <c r="AA29" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB29" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC29" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD29" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE29" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF29" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG29" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH29" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI29" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ29" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK29" s="35" t="s">
+        <v>11</v>
+      </c>
       <c r="AL29" s="35"/>
       <c r="AM29" s="35"/>
       <c r="AN29" s="35"/>
@@ -10607,11 +11153,11 @@
       </c>
       <c r="F30" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>CON FALTAS</v>
+        <v>REVISAR FALTAS</v>
       </c>
       <c r="G30" s="41">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H30" s="42">
         <f t="shared" si="4"/>
@@ -10619,7 +11165,7 @@
       </c>
       <c r="I30" s="42">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J30" s="42">
         <f t="shared" si="6"/>
@@ -10643,7 +11189,7 @@
       </c>
       <c r="O30" s="43">
         <f t="shared" si="11"/>
-        <v>0.22222222222222221</v>
+        <v>0.18181818181818182</v>
       </c>
       <c r="P30" s="35" t="s">
         <v>38</v>
@@ -10669,22 +11215,48 @@
       <c r="W30" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="X30" s="35"/>
-      <c r="Y30" s="35"/>
+      <c r="X30" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y30" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z30" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="AA30" s="35"/>
-      <c r="AB30" s="35"/>
-      <c r="AC30" s="35"/>
-      <c r="AD30" s="35"/>
-      <c r="AE30" s="35"/>
-      <c r="AF30" s="35"/>
-      <c r="AG30" s="35"/>
-      <c r="AH30" s="35"/>
-      <c r="AI30" s="35"/>
-      <c r="AJ30" s="35"/>
-      <c r="AK30" s="35"/>
+      <c r="AA30" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB30" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC30" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD30" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE30" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF30" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG30" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH30" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI30" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ30" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK30" s="35" t="s">
+        <v>11</v>
+      </c>
       <c r="AL30" s="35"/>
       <c r="AM30" s="35"/>
       <c r="AN30" s="35"/>
@@ -10809,7 +11381,7 @@
       </c>
       <c r="G31" s="41">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H31" s="42">
         <f t="shared" si="4"/>
@@ -10817,7 +11389,7 @@
       </c>
       <c r="I31" s="42">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="42">
         <f t="shared" si="6"/>
@@ -10841,7 +11413,7 @@
       </c>
       <c r="O31" s="43">
         <f t="shared" si="11"/>
-        <v>0.1111111111111111</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="P31" s="35" t="s">
         <v>38</v>
@@ -10867,22 +11439,48 @@
       <c r="W31" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="X31" s="35"/>
-      <c r="Y31" s="35"/>
+      <c r="X31" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y31" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z31" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="AA31" s="35"/>
-      <c r="AB31" s="35"/>
-      <c r="AC31" s="35"/>
-      <c r="AD31" s="35"/>
-      <c r="AE31" s="35"/>
-      <c r="AF31" s="35"/>
-      <c r="AG31" s="35"/>
-      <c r="AH31" s="35"/>
-      <c r="AI31" s="35"/>
-      <c r="AJ31" s="35"/>
-      <c r="AK31" s="35"/>
+      <c r="AA31" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB31" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC31" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD31" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE31" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF31" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG31" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH31" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI31" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ31" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK31" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AL31" s="35"/>
       <c r="AM31" s="35"/>
       <c r="AN31" s="35"/>
@@ -11002,11 +11600,11 @@
       </c>
       <c r="F32" s="30" t="str">
         <f t="shared" si="2"/>
-        <v>CON FALTAS</v>
+        <v>REVISAR FALTAS</v>
       </c>
       <c r="G32" s="41">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H32" s="42">
         <f t="shared" si="4"/>
@@ -11014,7 +11612,7 @@
       </c>
       <c r="I32" s="42">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J32" s="42">
         <f t="shared" si="6"/>
@@ -11038,7 +11636,7 @@
       </c>
       <c r="O32" s="43">
         <f t="shared" si="11"/>
-        <v>0.1111111111111111</v>
+        <v>0.13636363636363635</v>
       </c>
       <c r="P32" s="35" t="s">
         <v>38</v>
@@ -11064,22 +11662,48 @@
       <c r="W32" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="X32" s="35"/>
-      <c r="Y32" s="35"/>
+      <c r="X32" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y32" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z32" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="AA32" s="35"/>
-      <c r="AB32" s="35"/>
-      <c r="AC32" s="35"/>
-      <c r="AD32" s="35"/>
-      <c r="AE32" s="35"/>
-      <c r="AF32" s="35"/>
-      <c r="AG32" s="35"/>
-      <c r="AH32" s="35"/>
-      <c r="AI32" s="35"/>
-      <c r="AJ32" s="35"/>
-      <c r="AK32" s="35"/>
+      <c r="AA32" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB32" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC32" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD32" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE32" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF32" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG32" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH32" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI32" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ32" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK32" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AL32" s="35"/>
       <c r="AM32" s="35"/>
       <c r="AN32" s="35"/>
@@ -11200,15 +11824,15 @@
       <c r="F33" s="30"/>
       <c r="G33" s="41">
         <f t="shared" ref="G33" si="37">COUNTIF(P33:CR33,"A")</f>
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H33" s="42">
         <f t="shared" ref="H33" si="38">COUNTIF(P33:CR33,"CE")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I33" s="42">
         <f t="shared" ref="I33" si="39">COUNTIF(P33:CR33,"SE")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J33" s="42">
         <f t="shared" ref="J33" si="40">COUNTIF(P33:CR33,"INC")</f>
@@ -11232,7 +11856,7 @@
       </c>
       <c r="O33" s="43">
         <f t="shared" ref="O33" si="45">IFERROR(SUM(H33:K33)/SUM(G33:K33)," ")</f>
-        <v>0.33333333333333331</v>
+        <v>0.22727272727272727</v>
       </c>
       <c r="P33" s="35" t="s">
         <v>38</v>
@@ -11244,36 +11868,62 @@
         <v>38</v>
       </c>
       <c r="S33" s="35" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T33" s="35" t="s">
         <v>38</v>
       </c>
       <c r="U33" s="35" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V33" s="35" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W33" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="X33" s="35"/>
-      <c r="Y33" s="35"/>
+      <c r="X33" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y33" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="Z33" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="AA33" s="35"/>
-      <c r="AB33" s="35"/>
-      <c r="AC33" s="35"/>
-      <c r="AD33" s="35"/>
-      <c r="AE33" s="35"/>
-      <c r="AF33" s="35"/>
-      <c r="AG33" s="35"/>
-      <c r="AH33" s="35"/>
-      <c r="AI33" s="35"/>
-      <c r="AJ33" s="35"/>
-      <c r="AK33" s="35"/>
+      <c r="AA33" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB33" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC33" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD33" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE33" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF33" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG33" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH33" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI33" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ33" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK33" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AL33" s="35"/>
       <c r="AM33" s="35"/>
       <c r="AN33" s="35"/>
@@ -11378,20 +12028,20 @@
       <c r="D34" s="82"/>
       <c r="E34" s="82"/>
       <c r="F34" s="81"/>
-      <c r="G34" s="197" t="s">
+      <c r="G34" s="128" t="s">
         <v>59</v>
       </c>
-      <c r="H34" s="158"/>
-      <c r="I34" s="158"/>
-      <c r="J34" s="158"/>
-      <c r="K34" s="158"/>
-      <c r="L34" s="158"/>
-      <c r="M34" s="159"/>
-      <c r="N34" s="160" t="str">
+      <c r="H34" s="129"/>
+      <c r="I34" s="129"/>
+      <c r="J34" s="129"/>
+      <c r="K34" s="129"/>
+      <c r="L34" s="129"/>
+      <c r="M34" s="130"/>
+      <c r="N34" s="131" t="str">
         <f>G8</f>
         <v>A</v>
       </c>
-      <c r="O34" s="161"/>
+      <c r="O34" s="132"/>
       <c r="P34" s="44">
         <f t="shared" ref="P34:AU34" si="47">COUNTIF(P9:P33,"A")</f>
         <v>25</v>
@@ -11426,11 +12076,11 @@
       </c>
       <c r="X34" s="44">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y34" s="44">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Z34" s="44">
         <f t="shared" si="47"/>
@@ -11438,47 +12088,47 @@
       </c>
       <c r="AA34" s="44">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AB34" s="44">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC34" s="44">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AD34" s="44">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AE34" s="44">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AF34" s="44">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AG34" s="44">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AH34" s="44">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI34" s="44">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AJ34" s="44">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AK34" s="44">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL34" s="44">
         <f t="shared" si="47"/>
@@ -11776,20 +12426,20 @@
       <c r="D35" s="82"/>
       <c r="E35" s="82"/>
       <c r="F35" s="81"/>
-      <c r="G35" s="167" t="s">
+      <c r="G35" s="164" t="s">
         <v>10</v>
       </c>
-      <c r="H35" s="158"/>
-      <c r="I35" s="158"/>
-      <c r="J35" s="158"/>
-      <c r="K35" s="158"/>
-      <c r="L35" s="158"/>
-      <c r="M35" s="159"/>
-      <c r="N35" s="160" t="str">
+      <c r="H35" s="129"/>
+      <c r="I35" s="129"/>
+      <c r="J35" s="129"/>
+      <c r="K35" s="129"/>
+      <c r="L35" s="129"/>
+      <c r="M35" s="130"/>
+      <c r="N35" s="131" t="str">
         <f>H8</f>
         <v>CE</v>
       </c>
-      <c r="O35" s="161"/>
+      <c r="O35" s="132"/>
       <c r="P35" s="44">
         <f t="shared" ref="P35:AU35" si="51">COUNTIF(P9:P33,"CE")</f>
         <v>0</v>
@@ -11804,7 +12454,7 @@
       </c>
       <c r="S35" s="44">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T35" s="44">
         <f t="shared" si="51"/>
@@ -11812,15 +12462,15 @@
       </c>
       <c r="U35" s="44">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="44">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="44">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" s="44">
         <f t="shared" si="51"/>
@@ -11832,47 +12482,47 @@
       </c>
       <c r="Z35" s="44">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA35" s="44">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB35" s="44">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC35" s="44">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD35" s="44">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE35" s="44">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF35" s="44">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AG35" s="44">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH35" s="44">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI35" s="44">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ35" s="44">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK35" s="44">
         <f t="shared" si="51"/>
@@ -12174,20 +12824,20 @@
       <c r="D36" s="82"/>
       <c r="E36" s="82"/>
       <c r="F36" s="81"/>
-      <c r="G36" s="168" t="s">
+      <c r="G36" s="165" t="s">
         <v>12</v>
       </c>
-      <c r="H36" s="158"/>
-      <c r="I36" s="158"/>
-      <c r="J36" s="158"/>
-      <c r="K36" s="158"/>
-      <c r="L36" s="158"/>
-      <c r="M36" s="159"/>
-      <c r="N36" s="160" t="str">
+      <c r="H36" s="129"/>
+      <c r="I36" s="129"/>
+      <c r="J36" s="129"/>
+      <c r="K36" s="129"/>
+      <c r="L36" s="129"/>
+      <c r="M36" s="130"/>
+      <c r="N36" s="131" t="str">
         <f>I8</f>
         <v>SE</v>
       </c>
-      <c r="O36" s="161"/>
+      <c r="O36" s="132"/>
       <c r="P36" s="44">
         <f t="shared" ref="P36:AU36" si="55">COUNTIF(P9:P33,"SE")</f>
         <v>0</v>
@@ -12202,7 +12852,7 @@
       </c>
       <c r="S36" s="44">
         <f t="shared" si="55"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T36" s="44">
         <f t="shared" si="55"/>
@@ -12210,15 +12860,15 @@
       </c>
       <c r="U36" s="44">
         <f t="shared" si="55"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" s="44">
         <f t="shared" si="55"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W36" s="44">
         <f t="shared" si="55"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X36" s="44">
         <f t="shared" si="55"/>
@@ -12230,19 +12880,19 @@
       </c>
       <c r="Z36" s="44">
         <f t="shared" si="55"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA36" s="44">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB36" s="44">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC36" s="44">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD36" s="44">
         <f t="shared" si="55"/>
@@ -12254,27 +12904,27 @@
       </c>
       <c r="AF36" s="44">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG36" s="44">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH36" s="44">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI36" s="44">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ36" s="44">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AK36" s="44">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL36" s="44">
         <f t="shared" si="55"/>
@@ -12572,20 +13222,20 @@
       <c r="D37" s="82"/>
       <c r="E37" s="82"/>
       <c r="F37" s="45"/>
-      <c r="G37" s="169" t="s">
+      <c r="G37" s="166" t="s">
         <v>60</v>
       </c>
-      <c r="H37" s="158"/>
-      <c r="I37" s="158"/>
-      <c r="J37" s="158"/>
-      <c r="K37" s="158"/>
-      <c r="L37" s="158"/>
-      <c r="M37" s="159"/>
-      <c r="N37" s="160" t="str">
+      <c r="H37" s="129"/>
+      <c r="I37" s="129"/>
+      <c r="J37" s="129"/>
+      <c r="K37" s="129"/>
+      <c r="L37" s="129"/>
+      <c r="M37" s="130"/>
+      <c r="N37" s="131" t="str">
         <f>J8</f>
         <v>INC</v>
       </c>
-      <c r="O37" s="161"/>
+      <c r="O37" s="132"/>
       <c r="P37" s="44">
         <f t="shared" ref="P37:AU37" si="59">COUNTIF(P9:P33,"INC")</f>
         <v>0</v>
@@ -12970,20 +13620,20 @@
       <c r="D38" s="82"/>
       <c r="E38" s="82"/>
       <c r="F38" s="81"/>
-      <c r="G38" s="164" t="s">
+      <c r="G38" s="160" t="s">
         <v>61</v>
       </c>
-      <c r="H38" s="158"/>
-      <c r="I38" s="158"/>
-      <c r="J38" s="158"/>
-      <c r="K38" s="158"/>
-      <c r="L38" s="158"/>
-      <c r="M38" s="159"/>
-      <c r="N38" s="160" t="str">
+      <c r="H38" s="129"/>
+      <c r="I38" s="129"/>
+      <c r="J38" s="129"/>
+      <c r="K38" s="129"/>
+      <c r="L38" s="129"/>
+      <c r="M38" s="130"/>
+      <c r="N38" s="131" t="str">
         <f>K8</f>
         <v>LIC</v>
       </c>
-      <c r="O38" s="161"/>
+      <c r="O38" s="132"/>
       <c r="P38" s="44">
         <f t="shared" ref="P38:AU38" si="63">COUNTIF(P9:P33,"LIC")</f>
         <v>0</v>
@@ -13368,20 +14018,20 @@
       <c r="D39" s="82"/>
       <c r="E39" s="82"/>
       <c r="F39" s="81"/>
-      <c r="G39" s="157" t="s">
+      <c r="G39" s="168" t="s">
         <v>62</v>
       </c>
-      <c r="H39" s="158"/>
-      <c r="I39" s="158"/>
-      <c r="J39" s="158"/>
-      <c r="K39" s="158"/>
-      <c r="L39" s="158"/>
-      <c r="M39" s="159"/>
-      <c r="N39" s="160" t="str">
+      <c r="H39" s="129"/>
+      <c r="I39" s="129"/>
+      <c r="J39" s="129"/>
+      <c r="K39" s="129"/>
+      <c r="L39" s="129"/>
+      <c r="M39" s="130"/>
+      <c r="N39" s="131" t="str">
         <f>L8</f>
         <v>CLM</v>
       </c>
-      <c r="O39" s="161"/>
+      <c r="O39" s="132"/>
       <c r="P39" s="44">
         <f t="shared" ref="P39:AU39" si="67">COUNTIF(P9:P33,"CLM")</f>
         <v>0</v>
@@ -13766,20 +14416,20 @@
       <c r="D40" s="82"/>
       <c r="E40" s="82"/>
       <c r="F40" s="81"/>
-      <c r="G40" s="162" t="s">
+      <c r="G40" s="169" t="s">
         <v>63</v>
       </c>
-      <c r="H40" s="158"/>
-      <c r="I40" s="158"/>
-      <c r="J40" s="158"/>
-      <c r="K40" s="158"/>
-      <c r="L40" s="158"/>
-      <c r="M40" s="159"/>
-      <c r="N40" s="160" t="str">
+      <c r="H40" s="129"/>
+      <c r="I40" s="129"/>
+      <c r="J40" s="129"/>
+      <c r="K40" s="129"/>
+      <c r="L40" s="129"/>
+      <c r="M40" s="130"/>
+      <c r="N40" s="131" t="str">
         <f>M8</f>
         <v>SFF</v>
       </c>
-      <c r="O40" s="161"/>
+      <c r="O40" s="132"/>
       <c r="P40" s="44">
         <f t="shared" ref="P40:AU40" si="71">COUNTIF(P9:P33,"SFF")</f>
         <v>0</v>
@@ -14164,20 +14814,20 @@
       <c r="D41" s="82"/>
       <c r="E41" s="82"/>
       <c r="F41" s="81"/>
-      <c r="G41" s="163" t="s">
+      <c r="G41" s="170" t="s">
         <v>64</v>
       </c>
-      <c r="H41" s="158"/>
-      <c r="I41" s="158"/>
-      <c r="J41" s="158"/>
-      <c r="K41" s="158"/>
-      <c r="L41" s="158"/>
-      <c r="M41" s="159"/>
-      <c r="N41" s="160" t="str">
+      <c r="H41" s="129"/>
+      <c r="I41" s="129"/>
+      <c r="J41" s="129"/>
+      <c r="K41" s="129"/>
+      <c r="L41" s="129"/>
+      <c r="M41" s="130"/>
+      <c r="N41" s="131" t="str">
         <f>N8</f>
         <v>RET</v>
       </c>
-      <c r="O41" s="161"/>
+      <c r="O41" s="132"/>
       <c r="P41" s="44">
         <f t="shared" ref="P41:AU41" si="75">COUNTIF(P9:P33,"RET")</f>
         <v>0</v>
@@ -39518,11 +40168,65 @@
   </sheetData>
   <autoFilter ref="A8:DW41" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="80">
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="G6:O7"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="G34:M34"/>
-    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="AL1:AT1"/>
+    <mergeCell ref="AU1:BU1"/>
+    <mergeCell ref="BV1:CR1"/>
+    <mergeCell ref="AL3:AT3"/>
+    <mergeCell ref="CS1:CW5"/>
+    <mergeCell ref="AU2:BU2"/>
+    <mergeCell ref="BV2:CR2"/>
+    <mergeCell ref="BV3:CR3"/>
+    <mergeCell ref="AL2:AT2"/>
+    <mergeCell ref="AL4:AT5"/>
+    <mergeCell ref="CY1:DG1"/>
+    <mergeCell ref="CY2:DG2"/>
+    <mergeCell ref="CY4:CZ4"/>
+    <mergeCell ref="DA4:DG4"/>
+    <mergeCell ref="AU3:BU3"/>
+    <mergeCell ref="AU4:BU5"/>
+    <mergeCell ref="BV4:CR5"/>
+    <mergeCell ref="DJ4:DK4"/>
+    <mergeCell ref="DL4:DR4"/>
+    <mergeCell ref="CX6:DW6"/>
+    <mergeCell ref="DL7:DM7"/>
+    <mergeCell ref="DN7:DO7"/>
+    <mergeCell ref="DP7:DQ7"/>
+    <mergeCell ref="DR7:DS7"/>
+    <mergeCell ref="DT7:DU7"/>
+    <mergeCell ref="DV7:DW7"/>
+    <mergeCell ref="CX7:CY7"/>
+    <mergeCell ref="CZ7:DA7"/>
+    <mergeCell ref="DB7:DC7"/>
+    <mergeCell ref="DD7:DE7"/>
+    <mergeCell ref="DF7:DG7"/>
+    <mergeCell ref="DH7:DI7"/>
+    <mergeCell ref="DJ7:DK7"/>
+    <mergeCell ref="G39:M39"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="G40:M40"/>
+    <mergeCell ref="N40:O40"/>
+    <mergeCell ref="G41:M41"/>
+    <mergeCell ref="N41:O41"/>
+    <mergeCell ref="G38:M38"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="T2:W2"/>
+    <mergeCell ref="X2:AA2"/>
+    <mergeCell ref="T3:W3"/>
+    <mergeCell ref="X3:AA3"/>
+    <mergeCell ref="N35:O35"/>
+    <mergeCell ref="G35:M35"/>
+    <mergeCell ref="G36:M36"/>
+    <mergeCell ref="N36:O36"/>
+    <mergeCell ref="G37:M37"/>
+    <mergeCell ref="N37:O37"/>
+    <mergeCell ref="G2:O2"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="P1:S1"/>
+    <mergeCell ref="T1:W1"/>
+    <mergeCell ref="G1:O1"/>
     <mergeCell ref="X1:AA1"/>
     <mergeCell ref="AB1:AK1"/>
     <mergeCell ref="AB2:AK2"/>
@@ -39539,65 +40243,11 @@
     <mergeCell ref="AB3:AK3"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="P1:S1"/>
-    <mergeCell ref="T1:W1"/>
-    <mergeCell ref="G1:O1"/>
-    <mergeCell ref="G38:M38"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="T2:W2"/>
-    <mergeCell ref="X2:AA2"/>
-    <mergeCell ref="T3:W3"/>
-    <mergeCell ref="X3:AA3"/>
-    <mergeCell ref="N35:O35"/>
-    <mergeCell ref="G35:M35"/>
-    <mergeCell ref="G36:M36"/>
-    <mergeCell ref="N36:O36"/>
-    <mergeCell ref="G37:M37"/>
-    <mergeCell ref="N37:O37"/>
-    <mergeCell ref="G2:O2"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="G39:M39"/>
-    <mergeCell ref="N39:O39"/>
-    <mergeCell ref="G40:M40"/>
-    <mergeCell ref="N40:O40"/>
-    <mergeCell ref="G41:M41"/>
-    <mergeCell ref="N41:O41"/>
-    <mergeCell ref="DJ4:DK4"/>
-    <mergeCell ref="DL4:DR4"/>
-    <mergeCell ref="CX6:DW6"/>
-    <mergeCell ref="DL7:DM7"/>
-    <mergeCell ref="DN7:DO7"/>
-    <mergeCell ref="DP7:DQ7"/>
-    <mergeCell ref="DR7:DS7"/>
-    <mergeCell ref="DT7:DU7"/>
-    <mergeCell ref="DV7:DW7"/>
-    <mergeCell ref="CX7:CY7"/>
-    <mergeCell ref="CZ7:DA7"/>
-    <mergeCell ref="DB7:DC7"/>
-    <mergeCell ref="DD7:DE7"/>
-    <mergeCell ref="DF7:DG7"/>
-    <mergeCell ref="DH7:DI7"/>
-    <mergeCell ref="DJ7:DK7"/>
-    <mergeCell ref="CY1:DG1"/>
-    <mergeCell ref="CY2:DG2"/>
-    <mergeCell ref="CY4:CZ4"/>
-    <mergeCell ref="DA4:DG4"/>
-    <mergeCell ref="AU3:BU3"/>
-    <mergeCell ref="AU4:BU5"/>
-    <mergeCell ref="BV4:CR5"/>
-    <mergeCell ref="AL1:AT1"/>
-    <mergeCell ref="AU1:BU1"/>
-    <mergeCell ref="BV1:CR1"/>
-    <mergeCell ref="AL3:AT3"/>
-    <mergeCell ref="CS1:CW5"/>
-    <mergeCell ref="AU2:BU2"/>
-    <mergeCell ref="BV2:CR2"/>
-    <mergeCell ref="BV3:CR3"/>
-    <mergeCell ref="AL2:AT2"/>
-    <mergeCell ref="AL4:AT5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="G6:O7"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="G34:M34"/>
+    <mergeCell ref="N34:O34"/>
   </mergeCells>
   <conditionalFormatting sqref="E9:E33">
     <cfRule type="containsText" dxfId="78" priority="1" operator="containsText" text="RETIRADO">
@@ -39664,7 +40314,7 @@
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P34:CW41 G9:O33">
+  <conditionalFormatting sqref="G9:O33 P34:CW41">
     <cfRule type="cellIs" dxfId="65" priority="14" operator="equal">
       <formula>0</formula>
     </cfRule>
@@ -39963,18 +40613,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A1" s="204">
-        <v>0</v>
-      </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="130"/>
+      <c r="A1" s="200">
+        <v>0</v>
+      </c>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="194"/>
       <c r="L1" s="49"/>
       <c r="M1" s="49"/>
       <c r="N1" s="49"/>
@@ -39992,16 +40642,16 @@
       <c r="Z1" s="49"/>
     </row>
     <row r="2" spans="1:26" ht="15.75">
-      <c r="A2" s="144"/>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="130"/>
+      <c r="A2" s="143"/>
+      <c r="B2" s="143"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="194"/>
       <c r="L2" s="49"/>
       <c r="M2" s="49"/>
       <c r="N2" s="49"/>
@@ -40022,12 +40672,12 @@
       <c r="A3" s="198" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="174"/>
-      <c r="C3" s="205" t="s">
+      <c r="B3" s="120"/>
+      <c r="C3" s="201" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="124"/>
-      <c r="E3" s="174"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="120"/>
       <c r="F3" s="50"/>
       <c r="G3" s="50"/>
       <c r="H3" s="51"/>
@@ -40054,12 +40704,12 @@
       <c r="A4" s="198" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="174"/>
-      <c r="C4" s="206">
+      <c r="B4" s="120"/>
+      <c r="C4" s="202">
         <v>3414936</v>
       </c>
-      <c r="D4" s="124"/>
-      <c r="E4" s="174"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="120"/>
       <c r="F4" s="52" t="s">
         <v>65</v>
       </c>
@@ -40092,12 +40742,12 @@
       <c r="A5" s="198" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="174"/>
-      <c r="C5" s="203" t="s">
+      <c r="B5" s="120"/>
+      <c r="C5" s="199" t="s">
         <v>89</v>
       </c>
-      <c r="D5" s="124"/>
-      <c r="E5" s="174"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="120"/>
       <c r="F5" s="52" t="s">
         <v>67</v>
       </c>
@@ -40128,12 +40778,12 @@
       <c r="A6" s="198" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="174"/>
-      <c r="C6" s="199" t="s">
+      <c r="B6" s="120"/>
+      <c r="C6" s="203" t="s">
         <v>90</v>
       </c>
-      <c r="D6" s="124"/>
-      <c r="E6" s="174"/>
+      <c r="D6" s="119"/>
+      <c r="E6" s="120"/>
       <c r="F6" s="52" t="s">
         <v>69</v>
       </c>
@@ -40164,12 +40814,12 @@
       <c r="A7" s="198" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="174"/>
-      <c r="C7" s="200" t="s">
+      <c r="B7" s="120"/>
+      <c r="C7" s="204" t="s">
         <v>91</v>
       </c>
-      <c r="D7" s="124"/>
-      <c r="E7" s="174"/>
+      <c r="D7" s="119"/>
+      <c r="E7" s="120"/>
       <c r="F7" s="56" t="s">
         <v>70</v>
       </c>
@@ -40197,17 +40847,17 @@
       <c r="Z7" s="49"/>
     </row>
     <row r="8" spans="1:26" ht="15.75">
-      <c r="A8" s="201" t="s">
+      <c r="A8" s="205" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="174"/>
-      <c r="C8" s="202" t="s">
+      <c r="B8" s="120"/>
+      <c r="C8" s="206" t="s">
         <v>92</v>
       </c>
-      <c r="D8" s="124"/>
-      <c r="E8" s="124"/>
-      <c r="F8" s="124"/>
-      <c r="G8" s="174"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="119"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="120"/>
       <c r="H8" s="51"/>
       <c r="I8" s="51"/>
       <c r="J8" s="49"/>
@@ -50480,6 +51130,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:G8"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="A1:J2"/>
@@ -50487,12 +51143,6 @@
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C4:E4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:G8"/>
   </mergeCells>
   <conditionalFormatting sqref="B46:B1000">
     <cfRule type="expression" dxfId="13" priority="1">
@@ -50666,9 +51316,9 @@
       <c r="A1" s="210" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
+      <c r="B1" s="181"/>
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
       <c r="E1" s="70"/>
       <c r="F1" s="70"/>
     </row>
